--- a/research/traditional_assets/database/data/china/china_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/china/china_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.09449999999999999</v>
+        <v>-0.1233</v>
       </c>
       <c r="E2">
-        <v>0.043825</v>
+        <v>-0.01935</v>
       </c>
       <c r="F2">
-        <v>-0.08349999999999999</v>
+        <v>-0.03625</v>
       </c>
       <c r="G2">
-        <v>-0.007422638496318689</v>
+        <v>0.0466156867195058</v>
       </c>
       <c r="H2">
-        <v>-0.007596539612714868</v>
+        <v>0.04649163465995312</v>
       </c>
       <c r="I2">
-        <v>0.05706185086330502</v>
+        <v>0.04803281782810115</v>
       </c>
       <c r="J2">
-        <v>0.05398175487676769</v>
+        <v>0.0441773025186598</v>
       </c>
       <c r="K2">
-        <v>1369.45</v>
+        <v>-899.7599999999999</v>
       </c>
       <c r="L2">
-        <v>0.1677104815836268</v>
+        <v>-0.08652486907218676</v>
       </c>
       <c r="M2">
-        <v>722.7320000000001</v>
+        <v>6690.896</v>
       </c>
       <c r="N2">
-        <v>0.04341045600884148</v>
+        <v>0.2357432652165288</v>
       </c>
       <c r="O2">
-        <v>0.5277534776735187</v>
+        <v>-7.436311905396995</v>
       </c>
       <c r="P2">
-        <v>722.7320000000001</v>
+        <v>1556.196</v>
       </c>
       <c r="Q2">
-        <v>0.04341045600884148</v>
+        <v>0.05483013431338662</v>
       </c>
       <c r="R2">
-        <v>0.5277534776735187</v>
+        <v>-1.729567884769272</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>5134.7</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.7674159036398115</v>
       </c>
       <c r="U2">
-        <v>2669.697</v>
+        <v>2689.457</v>
       </c>
       <c r="V2">
-        <v>0.1603537191869684</v>
+        <v>0.09475881478944675</v>
       </c>
       <c r="W2">
-        <v>-0.01257785467128028</v>
+        <v>0.04656375002738439</v>
       </c>
       <c r="X2">
-        <v>0.04935442760262557</v>
+        <v>0.08012536483317503</v>
       </c>
       <c r="Y2">
-        <v>-0.06193228227390585</v>
+        <v>-0.03356161480579065</v>
       </c>
       <c r="Z2">
-        <v>0.05444920878021322</v>
+        <v>0.02865252739924236</v>
       </c>
       <c r="AA2">
-        <v>0.0002302401417780123</v>
+        <v>-0.241900653985194</v>
       </c>
       <c r="AB2">
-        <v>0.04889125496003793</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC2">
-        <v>-0.04850435736976863</v>
+        <v>-0.323134811908714</v>
       </c>
       <c r="AD2">
-        <v>155564.853</v>
+        <v>263748.66</v>
       </c>
       <c r="AE2">
-        <v>7.405165323155209</v>
+        <v>0.9822600003606849</v>
       </c>
       <c r="AF2">
-        <v>155572.2581653231</v>
+        <v>263749.6422600003</v>
       </c>
       <c r="AG2">
-        <v>152902.5611653232</v>
+        <v>261060.1852600003</v>
       </c>
       <c r="AH2">
-        <v>0.9033288949832254</v>
+        <v>0.9028447683713786</v>
       </c>
       <c r="AI2">
-        <v>0.8158259249734549</v>
+        <v>0.845209892900707</v>
       </c>
       <c r="AJ2">
-        <v>0.9018067452506833</v>
+        <v>0.9019420157190737</v>
       </c>
       <c r="AK2">
-        <v>0.8132108816264572</v>
+        <v>0.8438642192873825</v>
       </c>
       <c r="AL2">
-        <v>287.268</v>
+        <v>156.891</v>
       </c>
       <c r="AM2">
-        <v>277.681</v>
+        <v>-0.8550000000000182</v>
       </c>
       <c r="AN2">
-        <v>331.496873934538</v>
+        <v>522.9217546468401</v>
       </c>
       <c r="AO2">
-        <v>1.618982970605846</v>
+        <v>3.181367956096908</v>
       </c>
       <c r="AP2">
-        <v>325.8237324525297</v>
+        <v>517.5914453729871</v>
       </c>
       <c r="AQ2">
-        <v>1.674878727748748</v>
+        <v>-583.7754385964788</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bally, Corp. (OTCPK:BLYQ)</t>
+          <t>Yangzijiang Financial Holding Ltd. (SGX:YF8)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,80 +724,98 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="F3">
+        <v>0.011</v>
+      </c>
+      <c r="G3">
+        <v>1.171602787456446</v>
+      </c>
+      <c r="H3">
+        <v>1.171602787456446</v>
+      </c>
+      <c r="I3">
+        <v>0.9294425087108015</v>
+      </c>
+      <c r="J3">
+        <v>0.7358885017421604</v>
+      </c>
       <c r="K3">
-        <v>-0.03</v>
+        <v>192</v>
+      </c>
+      <c r="L3">
+        <v>0.8362369337979094</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>115.2</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1178878428162096</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>51.1</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.05229226361031519</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.2661458333333334</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>64.09999999999999</v>
+      </c>
+      <c r="T3">
+        <v>0.5564236111111112</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>323.2</v>
       </c>
       <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0.5084745762711864</v>
+        <v>0.3307408923454768</v>
       </c>
       <c r="X3">
-        <v>0.04895482598202832</v>
-      </c>
-      <c r="Y3">
-        <v>0.4595197502891581</v>
-      </c>
-      <c r="Z3">
-        <v>-0</v>
-      </c>
-      <c r="AA3">
-        <v>15.00000000000004</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AB3">
-        <v>0.04889125496003793</v>
-      </c>
-      <c r="AC3">
-        <v>14.95110874504</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AD3">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.089</v>
+        <v>-323.2</v>
       </c>
       <c r="AH3">
-        <v>0.002997743271918893</v>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.002997743271918893</v>
+        <v>-0.4941896024464832</v>
+      </c>
+      <c r="AK3">
+        <v>-0.1189065891615466</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>-1.508166122258516</v>
       </c>
     </row>
     <row r="4">
@@ -808,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anxin Trust Co., Ltd (SHSE:600816)</t>
+          <t>Hainan Haide Capital Management Co., Ltd. (SZSE:000567)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -817,43 +835,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.395</v>
+        <v>0.47</v>
+      </c>
+      <c r="E4">
+        <v>0.645</v>
       </c>
       <c r="G4">
-        <v>-5.925318761384336</v>
+        <v>0.5606975184439973</v>
       </c>
       <c r="H4">
-        <v>-5.925318761384336</v>
+        <v>0.5606975184439973</v>
       </c>
       <c r="I4">
-        <v>3.531240795483325</v>
+        <v>0.8685446009389671</v>
       </c>
       <c r="J4">
-        <v>3.531240795483325</v>
+        <v>0.7865153886280647</v>
       </c>
       <c r="K4">
-        <v>-735.8</v>
+        <v>97.8</v>
       </c>
       <c r="L4">
-        <v>-13.40255009107468</v>
+        <v>0.6559356136820925</v>
       </c>
       <c r="M4">
-        <v>19.7</v>
+        <v>56.4</v>
       </c>
       <c r="N4">
-        <v>0.004963591927234246</v>
+        <v>0.03006076111288775</v>
       </c>
       <c r="O4">
-        <v>-0.02677357977711335</v>
+        <v>0.5766871165644172</v>
       </c>
       <c r="P4">
-        <v>19.7</v>
+        <v>56.4</v>
       </c>
       <c r="Q4">
-        <v>0.004963591927234246</v>
+        <v>0.03006076111288775</v>
       </c>
       <c r="R4">
-        <v>-0.02677357977711335</v>
+        <v>0.5766871165644172</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -862,73 +883,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>144.9</v>
+        <v>18.3</v>
       </c>
       <c r="V4">
-        <v>0.03650885635818489</v>
+        <v>0.009753757595139112</v>
       </c>
       <c r="W4">
-        <v>-1.309485673607403</v>
+        <v>0.1373402611992698</v>
       </c>
       <c r="X4">
-        <v>0.04893415030055481</v>
+        <v>0.08447386726560092</v>
       </c>
       <c r="Y4">
-        <v>-1.358419823907958</v>
+        <v>0.05286639393366883</v>
       </c>
       <c r="Z4">
-        <v>0.1021919328914005</v>
+        <v>0.1701083856246434</v>
       </c>
       <c r="AA4">
-        <v>0.3608643223954076</v>
+        <v>0.1337928630284592</v>
       </c>
       <c r="AB4">
-        <v>0.04888784184201058</v>
+        <v>0.07920480662503081</v>
       </c>
       <c r="AC4">
-        <v>0.3119764805533971</v>
+        <v>0.05458805640342836</v>
       </c>
       <c r="AD4">
-        <v>2.37</v>
+        <v>314</v>
       </c>
       <c r="AE4">
-        <v>6.324401639827222</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>8.694401639827223</v>
+        <v>314</v>
       </c>
       <c r="AG4">
-        <v>-136.2055983601728</v>
+        <v>295.7</v>
       </c>
       <c r="AH4">
-        <v>0.002185844196744348</v>
+        <v>0.1433659026572916</v>
       </c>
       <c r="AI4">
-        <v>-0.3435762125076208</v>
+        <v>0.308903098868667</v>
       </c>
       <c r="AJ4">
-        <v>-0.03553781859098834</v>
+        <v>0.1361480731157051</v>
       </c>
       <c r="AK4">
-        <v>0.8002415882463957</v>
+        <v>0.2962332197956321</v>
       </c>
       <c r="AL4">
-        <v>218.2</v>
+        <v>19.4</v>
       </c>
       <c r="AM4">
-        <v>215.54</v>
+        <v>19.4</v>
       </c>
       <c r="AN4">
-        <v>0.01212090216335089</v>
+        <v>2.42283950617284</v>
       </c>
       <c r="AO4">
-        <v>0.8863428047662696</v>
+        <v>6.675257731958763</v>
       </c>
       <c r="AP4">
-        <v>-0.6965969332592072</v>
+        <v>2.281635802469136</v>
       </c>
       <c r="AQ4">
-        <v>0.8972812471003062</v>
+        <v>6.675257731958763</v>
       </c>
     </row>
     <row r="5">
@@ -939,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shaanxi International Trust Co., Ltd. (SZSE:000563)</t>
+          <t>Shaanxi International Trust Co.,Ltd. (SZSE:000563)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -948,46 +969,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.177</v>
+        <v>0.0862</v>
       </c>
       <c r="E5">
-        <v>0.0965</v>
+        <v>0.0575</v>
       </c>
       <c r="G5">
-        <v>0.5996095928611265</v>
+        <v>0.6256097560975609</v>
       </c>
       <c r="H5">
-        <v>0.595649749023982</v>
+        <v>0.6208425720620842</v>
       </c>
       <c r="I5">
-        <v>0.6182375906302287</v>
+        <v>0.5698447893569843</v>
       </c>
       <c r="J5">
-        <v>0.4629649986525641</v>
+        <v>0.4252987940078956</v>
       </c>
       <c r="K5">
-        <v>113.6</v>
+        <v>107.1</v>
       </c>
       <c r="L5">
-        <v>0.316787506971556</v>
+        <v>0.3957871396895787</v>
       </c>
       <c r="M5">
-        <v>32.8</v>
+        <v>37</v>
       </c>
       <c r="N5">
-        <v>0.01627387744976433</v>
+        <v>0.01646933143416719</v>
       </c>
       <c r="O5">
-        <v>0.2887323943661972</v>
+        <v>0.3454715219421102</v>
       </c>
       <c r="P5">
-        <v>32.8</v>
+        <v>37</v>
       </c>
       <c r="Q5">
-        <v>0.01627387744976433</v>
+        <v>0.01646933143416719</v>
       </c>
       <c r="R5">
-        <v>0.2887323943661972</v>
+        <v>0.3454715219421102</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -996,73 +1017,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>73.40000000000001</v>
+        <v>147.7</v>
       </c>
       <c r="V5">
-        <v>0.03641776234185066</v>
+        <v>0.06574379061693225</v>
       </c>
       <c r="W5">
-        <v>0.06623134328358209</v>
+        <v>0.05701964542405366</v>
       </c>
       <c r="X5">
-        <v>0.04892151510726388</v>
+        <v>0.07944690035525567</v>
       </c>
       <c r="Y5">
-        <v>0.0173098281763182</v>
+        <v>-0.02242725493120201</v>
       </c>
       <c r="Z5">
-        <v>0.2338746494489011</v>
+        <v>0.1496424838661513</v>
       </c>
       <c r="AA5">
-        <v>0.1082757767669794</v>
+        <v>0.06364276792062012</v>
       </c>
       <c r="AB5">
-        <v>0.04887604406418831</v>
+        <v>0.07936495446768028</v>
       </c>
       <c r="AC5">
-        <v>0.05939973270279107</v>
+        <v>-0.01572218654706016</v>
       </c>
       <c r="AD5">
-        <v>3.41</v>
+        <v>4.92</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.41</v>
+        <v>4.92</v>
       </c>
       <c r="AG5">
-        <v>-69.99000000000001</v>
+        <v>-142.78</v>
       </c>
       <c r="AH5">
-        <v>0.001689030219276738</v>
+        <v>0.002185190449118818</v>
       </c>
       <c r="AI5">
-        <v>0.001812181473234452</v>
+        <v>0.002743973854167829</v>
       </c>
       <c r="AJ5">
-        <v>-0.03597514276462214</v>
+        <v>-0.06786702284415969</v>
       </c>
       <c r="AK5">
-        <v>-0.03870464688023625</v>
+        <v>-0.08677947147059539</v>
       </c>
       <c r="AL5">
-        <v>45</v>
+        <v>31.3</v>
       </c>
       <c r="AM5">
-        <v>45</v>
+        <v>31.3</v>
       </c>
       <c r="AN5">
-        <v>0.01536036036036036</v>
+        <v>0.03186528497409327</v>
       </c>
       <c r="AO5">
-        <v>4.926666666666667</v>
+        <v>4.926517571884983</v>
       </c>
       <c r="AP5">
-        <v>-0.3152702702702703</v>
+        <v>-0.924740932642487</v>
       </c>
       <c r="AQ5">
-        <v>4.926666666666667</v>
+        <v>4.926517571884983</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hainan Haide Capital Management Co., Ltd. (SZSE:000567)</t>
+          <t>Kunwu Jiuding Investment Holdings Co., Ltd. (SHSE:600053)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,46 +1103,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.8129999999999999</v>
+        <v>-0.171</v>
       </c>
       <c r="E6">
-        <v>0.879</v>
+        <v>-0.264</v>
       </c>
       <c r="G6">
-        <v>0.4612188365650969</v>
+        <v>-0.03512605042016807</v>
       </c>
       <c r="H6">
-        <v>0.4612188365650969</v>
+        <v>-0.03512605042016807</v>
       </c>
       <c r="I6">
-        <v>0.7202216066481995</v>
+        <v>0.4369747899159664</v>
       </c>
       <c r="J6">
-        <v>0.6447779656667609</v>
+        <v>0.3378830320006791</v>
       </c>
       <c r="K6">
-        <v>37.7</v>
+        <v>15.4</v>
       </c>
       <c r="L6">
-        <v>0.5221606648199446</v>
+        <v>0.2588235294117647</v>
       </c>
       <c r="M6">
-        <v>14.5</v>
+        <v>0.893</v>
       </c>
       <c r="N6">
-        <v>0.008048848182070497</v>
+        <v>0.000961248654467169</v>
       </c>
       <c r="O6">
-        <v>0.3846153846153846</v>
+        <v>0.05798701298701299</v>
       </c>
       <c r="P6">
-        <v>14.5</v>
+        <v>0.893</v>
       </c>
       <c r="Q6">
-        <v>0.008048848182070497</v>
+        <v>0.000961248654467169</v>
       </c>
       <c r="R6">
-        <v>0.3846153846153846</v>
+        <v>0.05798701298701299</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,73 +1151,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>96.3</v>
+        <v>35.5</v>
       </c>
       <c r="V6">
-        <v>0.05345545378850958</v>
+        <v>0.03821313240043057</v>
       </c>
       <c r="W6">
-        <v>0.05890625000000001</v>
+        <v>0.03610785463071512</v>
       </c>
       <c r="X6">
-        <v>0.05254480387615034</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y6">
-        <v>0.006361446123849666</v>
+        <v>-0.04327239339870214</v>
       </c>
       <c r="Z6">
-        <v>0.100097046998475</v>
+        <v>0.1349686849966995</v>
       </c>
       <c r="AA6">
-        <v>0.06454037033292687</v>
+        <v>0.04560362851182939</v>
       </c>
       <c r="AB6">
-        <v>0.04941009928538379</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC6">
-        <v>0.01513027104754308</v>
+        <v>-0.03377661951758787</v>
       </c>
       <c r="AD6">
-        <v>260.7</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>260.7</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>164.4</v>
+        <v>-35.5</v>
       </c>
       <c r="AH6">
-        <v>0.1264183881291824</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.2679893092105263</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0.08362582023500685</v>
+        <v>-0.03973139339675433</v>
       </c>
       <c r="AK6">
-        <v>0.187564175698802</v>
+        <v>-0.09494517250601765</v>
       </c>
       <c r="AL6">
-        <v>15.3</v>
+        <v>0.861</v>
       </c>
       <c r="AM6">
-        <v>10.44</v>
+        <v>-6.559</v>
       </c>
       <c r="AN6">
-        <v>5.013461538461538</v>
+        <v>0</v>
       </c>
       <c r="AO6">
-        <v>3.398692810457516</v>
+        <v>30.19744483159117</v>
       </c>
       <c r="AP6">
-        <v>3.161538461538461</v>
+        <v>-1.349809885931559</v>
       </c>
       <c r="AQ6">
-        <v>4.980842911877394</v>
+        <v>-3.964018905320933</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shanghai Greencourt Investment Group Co., Ltd. (SHSE:900919)</t>
+          <t>Shandong International Trust Co., Ltd. (SEHK:1697)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1215,119 +1236,86 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.09449999999999999</v>
-      </c>
-      <c r="G7">
-        <v>-0.1574074074074074</v>
-      </c>
-      <c r="H7">
-        <v>-0.1574074074074074</v>
-      </c>
-      <c r="I7">
-        <v>0.3261316872427983</v>
-      </c>
-      <c r="J7">
-        <v>0.3261316872427983</v>
-      </c>
       <c r="K7">
-        <v>-11.3</v>
-      </c>
-      <c r="L7">
-        <v>-1.162551440329218</v>
+        <v>-60.7</v>
       </c>
       <c r="M7">
-        <v>1.32</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.003727760519627224</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0.1168141592920354</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>1.32</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.003727760519627224</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0.1168141592920354</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>11.8</v>
+        <v>27.8</v>
       </c>
       <c r="V7">
-        <v>0.03332391979666761</v>
+        <v>0.1192621192621193</v>
       </c>
       <c r="W7">
-        <v>-0.1010733452593918</v>
+        <v>-0.03703025866276232</v>
       </c>
       <c r="X7">
-        <v>0.05026662063981496</v>
+        <v>0.1197385320252116</v>
       </c>
       <c r="Y7">
-        <v>-0.1513399658992067</v>
+        <v>-0.1567687906879739</v>
       </c>
       <c r="Z7">
-        <v>0.08993338267949667</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0.02933012583271651</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04897831887810943</v>
+        <v>0.07868261712126562</v>
       </c>
       <c r="AC7">
-        <v>-0.01964819304539293</v>
+        <v>-0.07868261712126562</v>
       </c>
       <c r="AD7">
-        <v>19.4</v>
+        <v>309.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>19.4</v>
+        <v>309.1</v>
       </c>
       <c r="AG7">
-        <v>7.599999999999998</v>
+        <v>281.3</v>
       </c>
       <c r="AH7">
-        <v>0.05194109772423025</v>
+        <v>0.5700848395426042</v>
       </c>
       <c r="AI7">
-        <v>0.1604631927212572</v>
+        <v>0.1691196585872955</v>
       </c>
       <c r="AJ7">
-        <v>0.02101188830522532</v>
+        <v>0.5468506998444791</v>
       </c>
       <c r="AK7">
-        <v>0.06966086159486708</v>
+        <v>0.1562864603589088</v>
       </c>
       <c r="AL7">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>2.13</v>
-      </c>
-      <c r="AN7">
-        <v>5.969230769230768</v>
-      </c>
-      <c r="AO7">
-        <v>1.488262910798122</v>
-      </c>
-      <c r="AP7">
-        <v>2.338461538461538</v>
-      </c>
-      <c r="AQ7">
-        <v>1.488262910798122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1338,7 +1326,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shandong International Trust Co., Ltd. (SEHK:1697)</t>
+          <t>China Cinda Asset Management Co., Ltd. (SEHK:1359)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1346,6 +1334,15 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D8">
+        <v>-0.0756</v>
+      </c>
+      <c r="E8">
+        <v>-0.09619999999999999</v>
+      </c>
+      <c r="F8">
+        <v>-0.08349999999999999</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1359,85 +1356,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>79.7</v>
+        <v>1475.2</v>
       </c>
       <c r="L8">
-        <v>0.3677895708352562</v>
+        <v>0.2011398652886477</v>
       </c>
       <c r="M8">
-        <v>40.4</v>
+        <v>3619.903</v>
       </c>
       <c r="N8">
-        <v>0.1711864406779661</v>
+        <v>0.6847835874541258</v>
       </c>
       <c r="O8">
-        <v>0.506900878293601</v>
+        <v>2.453838801518438</v>
       </c>
       <c r="P8">
-        <v>40.4</v>
+        <v>534.303</v>
       </c>
       <c r="Q8">
-        <v>0.1711864406779661</v>
+        <v>0.101075063372555</v>
       </c>
       <c r="R8">
-        <v>0.506900878293601</v>
+        <v>0.3621902114967462</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>3085.6</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.8523985311208615</v>
       </c>
       <c r="U8">
-        <v>213.2</v>
+        <v>2054.3</v>
       </c>
       <c r="V8">
-        <v>0.9033898305084745</v>
+        <v>0.3886156407249064</v>
       </c>
       <c r="W8">
-        <v>0.05591412936719517</v>
+        <v>0.06285765417211714</v>
       </c>
       <c r="X8">
-        <v>0.07547934194709964</v>
+        <v>0.8688941451403585</v>
       </c>
       <c r="Y8">
-        <v>-0.01956521257990447</v>
+        <v>-0.8060364909682414</v>
       </c>
       <c r="Z8">
-        <v>0.1535246191994332</v>
+        <v>0.04160686386746074</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04808754740385903</v>
+        <v>0.0795740455441699</v>
       </c>
       <c r="AC8">
-        <v>-0.04808754740385903</v>
+        <v>-0.0795740455441699</v>
       </c>
       <c r="AD8">
-        <v>247.8</v>
+        <v>137128.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>247.8</v>
+        <v>137128.4</v>
       </c>
       <c r="AG8">
-        <v>34.60000000000002</v>
+        <v>135074.1</v>
       </c>
       <c r="AH8">
-        <v>0.5121951219512195</v>
+        <v>0.9628816146659119</v>
       </c>
       <c r="AI8">
-        <v>0.1313195548489666</v>
+        <v>0.8154754825235374</v>
       </c>
       <c r="AJ8">
-        <v>0.1278640059127865</v>
+        <v>0.9623383535087913</v>
       </c>
       <c r="AK8">
-        <v>0.0206715258692795</v>
+        <v>0.8131933561825683</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1454,7 +1451,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kunwu Jiuding Investment Holdings Co., Ltd. (SHSE:600053)</t>
+          <t>China Huarong Asset Management Co., Ltd. (SEHK:2799)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1463,121 +1460,106 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.353</v>
-      </c>
-      <c r="E9">
-        <v>-0.476</v>
+        <v>-0.239</v>
       </c>
       <c r="G9">
-        <v>0.6357827476038338</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>0.6357827476038338</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.006038338658146965</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.006038338658146965</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>3.25</v>
+        <v>-2633.1</v>
       </c>
       <c r="L9">
-        <v>0.1038338658146965</v>
+        <v>-1.135593220338983</v>
       </c>
       <c r="M9">
-        <v>3.38</v>
+        <v>2803.1</v>
       </c>
       <c r="N9">
-        <v>0.00317281516943584</v>
+        <v>0.664304673428761</v>
       </c>
       <c r="O9">
-        <v>1.04</v>
+        <v>-1.064562682769359</v>
       </c>
       <c r="P9">
-        <v>3.38</v>
+        <v>876.5</v>
       </c>
       <c r="Q9">
-        <v>0.00317281516943584</v>
+        <v>0.2077211110057825</v>
       </c>
       <c r="R9">
-        <v>1.04</v>
+        <v>-0.332877596749079</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1926.6</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.6873104776854198</v>
       </c>
       <c r="U9">
-        <v>37</v>
+        <v>0.018</v>
       </c>
       <c r="V9">
-        <v>0.03473200037548109</v>
+        <v>4.265807185515214e-06</v>
       </c>
       <c r="W9">
-        <v>0.008042563721851026</v>
+        <v>-0.3803408926765853</v>
       </c>
       <c r="X9">
-        <v>0.0501010005958102</v>
+        <v>0.9880619788468232</v>
       </c>
       <c r="Y9">
-        <v>-0.04205843687395917</v>
+        <v>-1.368402871523408</v>
       </c>
       <c r="Z9">
-        <v>0.07661315984001801</v>
+        <v>0.01275064668825227</v>
       </c>
       <c r="AA9">
-        <v>0.0004626162047847733</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.0489669735745534</v>
+        <v>0.08247776862382139</v>
       </c>
       <c r="AC9">
-        <v>-0.04850435736976863</v>
+        <v>-0.08247776862382139</v>
       </c>
       <c r="AD9">
-        <v>51.4</v>
+        <v>125981.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>51.4</v>
+        <v>125981.6</v>
       </c>
       <c r="AG9">
-        <v>14.4</v>
+        <v>125981.582</v>
       </c>
       <c r="AH9">
-        <v>0.0460284767618877</v>
+        <v>0.9675916965435034</v>
       </c>
       <c r="AI9">
-        <v>0.1060449762739839</v>
+        <v>0.9273465109380302</v>
       </c>
       <c r="AJ9">
-        <v>0.01333703806612948</v>
+        <v>0.9675916920631334</v>
       </c>
       <c r="AK9">
-        <v>0.03216439580075944</v>
+        <v>0.927346501311629</v>
       </c>
       <c r="AL9">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>6.43</v>
-      </c>
-      <c r="AN9">
-        <v>263.5897435897436</v>
-      </c>
-      <c r="AO9">
-        <v>0.02939346811819596</v>
-      </c>
-      <c r="AP9">
-        <v>73.84615384615384</v>
-      </c>
-      <c r="AQ9">
-        <v>0.02939346811819596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1588,7 +1570,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wins Finance Holdings Inc. (OTCPK:WINS.F)</t>
+          <t>Puhui Wealth Investment Management Co., Ltd. (NasdaqCM:PHCF)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1597,22 +1579,22 @@
         </is>
       </c>
       <c r="G10">
-        <v>-0</v>
+        <v>-1.495901639344262</v>
       </c>
       <c r="H10">
-        <v>-0</v>
+        <v>-1.495901639344262</v>
       </c>
       <c r="I10">
-        <v>-0.0002578413799238582</v>
+        <v>-1.275185245931204</v>
       </c>
       <c r="J10">
-        <v>-0.0002578413799238582</v>
+        <v>-1.275185245931204</v>
       </c>
       <c r="K10">
-        <v>-216.5</v>
+        <v>-5.66</v>
       </c>
       <c r="L10">
-        <v>1.235025670279521</v>
+        <v>-2.319672131147541</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1636,67 +1618,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.007</v>
+        <v>0.952</v>
       </c>
       <c r="V10">
-        <v>0.000588235294117647</v>
+        <v>0.15787728026534</v>
       </c>
       <c r="W10">
-        <v>-1.102903718797758</v>
+        <v>-0.9085072231139647</v>
       </c>
       <c r="X10">
-        <v>0.04899361812161419</v>
+        <v>0.09766286111917769</v>
       </c>
       <c r="Y10">
-        <v>-1.151897336919373</v>
+        <v>-1.006170084233142</v>
       </c>
       <c r="Z10">
-        <v>-0.8929526433887505</v>
+        <v>0.3793968833266199</v>
       </c>
       <c r="AA10">
-        <v>0.0002302401417780123</v>
+        <v>-0.483801307970388</v>
       </c>
       <c r="AB10">
-        <v>0.04889764375841969</v>
+        <v>0.07999054722321847</v>
       </c>
       <c r="AC10">
-        <v>-0.04866740361664168</v>
+        <v>-0.5637918551936065</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AE10">
-        <v>0.0540020304967383</v>
+        <v>0.9822600003606849</v>
       </c>
       <c r="AF10">
-        <v>0.0540020304967383</v>
+        <v>3.622260000360685</v>
       </c>
       <c r="AG10">
-        <v>0.0470020304967383</v>
+        <v>2.670260000360685</v>
       </c>
       <c r="AH10">
-        <v>0.004517485471306574</v>
+        <v>0.3752758421577256</v>
       </c>
       <c r="AI10">
-        <v>-0.02080203109984383</v>
+        <v>0.5738451838412403</v>
       </c>
       <c r="AJ10">
-        <v>0.003934211308975899</v>
+        <v>0.3069172645702524</v>
       </c>
       <c r="AK10">
-        <v>-0.01805688327360003</v>
+        <v>0.4981586714414985</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>0.928</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>-0.9723756906077349</v>
+      </c>
+      <c r="AO10">
+        <v>-3.731182795698925</v>
       </c>
       <c r="AP10">
-        <v>0.839321973156041</v>
+        <v>-0.9835211787700499</v>
+      </c>
+      <c r="AQ10">
+        <v>-3.739224137931035</v>
       </c>
     </row>
     <row r="11">
@@ -1707,7 +1695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>China Cinda Asset Management Co., Ltd. (SEHK:1359)</t>
+          <t>Brilliant Acquisition Corporation (NasdaqCM:BRLI)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1715,113 +1703,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D11">
-        <v>-0.0457</v>
-      </c>
-      <c r="E11">
-        <v>-0.00885</v>
-      </c>
-      <c r="F11">
-        <v>-0.08349999999999999</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
       <c r="K11">
-        <v>2105.4</v>
-      </c>
-      <c r="L11">
-        <v>0.2774644175013179</v>
+        <v>-1.51</v>
       </c>
       <c r="M11">
-        <v>610.6320000000001</v>
+        <v>17.3</v>
       </c>
       <c r="N11">
-        <v>0.08786198362566369</v>
+        <v>0.7792792792792793</v>
       </c>
       <c r="O11">
-        <v>0.2900313479623824</v>
+        <v>-11.45695364238411</v>
       </c>
       <c r="P11">
-        <v>610.6320000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.08786198362566369</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.2900313479623824</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>2089.7</v>
+        <v>31.2</v>
       </c>
       <c r="V11">
-        <v>0.300680585332163</v>
+        <v>1.405405405405405</v>
       </c>
       <c r="W11">
-        <v>0.1019277878368303</v>
+        <v>125.8333333333333</v>
       </c>
       <c r="X11">
-        <v>0.6137961109634598</v>
+        <v>0.08415116908152444</v>
       </c>
       <c r="Y11">
-        <v>-0.5118683231266294</v>
+        <v>125.7491821642518</v>
       </c>
       <c r="Z11">
-        <v>0.05233966150282702</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>-2.308868501529052</v>
       </c>
       <c r="AB11">
-        <v>0.05071512359328965</v>
+        <v>0.07843182176665267</v>
       </c>
       <c r="AC11">
-        <v>-0.05071512359328965</v>
+        <v>-2.387300323295705</v>
       </c>
       <c r="AD11">
-        <v>154974.4</v>
+        <v>3.48</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>154974.4</v>
+        <v>3.48</v>
       </c>
       <c r="AG11">
-        <v>152884.7</v>
+        <v>-27.72</v>
       </c>
       <c r="AH11">
-        <v>0.9570793265742079</v>
+        <v>0.1355140186915888</v>
       </c>
       <c r="AI11">
-        <v>0.8363296870530967</v>
+        <v>-7.25</v>
       </c>
       <c r="AJ11">
-        <v>0.9565181756640928</v>
+        <v>5.021739130434783</v>
       </c>
       <c r="AK11">
-        <v>0.8344628910674061</v>
+        <v>0.875</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>-0.066</v>
+      </c>
+      <c r="AQ11">
+        <v>22.87878787878788</v>
       </c>
     </row>
     <row r="12">
@@ -1832,7 +1799,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shanghai Realway Capital Assets Management Co., Ltd. (SEHK:1835)</t>
+          <t>Anxin Trust Co., Ltd (SHSE:600816)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1840,23 +1807,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D12">
+        <v>-0.471</v>
+      </c>
       <c r="G12">
-        <v>0.2226720647773279</v>
+        <v>-0.6503067484662576</v>
       </c>
       <c r="H12">
-        <v>0.2226720647773279</v>
+        <v>-0.6503067484662576</v>
       </c>
       <c r="I12">
-        <v>-0.05546558704453441</v>
+        <v>-0.3466257668711656</v>
       </c>
       <c r="J12">
-        <v>-0.05546558704453441</v>
+        <v>-0.3466257668711656</v>
       </c>
       <c r="K12">
-        <v>-0.727</v>
+        <v>-79.8</v>
       </c>
       <c r="L12">
-        <v>-0.098110661268556</v>
+        <v>-2.447852760736196</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1880,73 +1850,64 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2.17</v>
+        <v>49.2</v>
       </c>
       <c r="V12">
-        <v>0.02726130653266332</v>
+        <v>0.01704604510965596</v>
       </c>
       <c r="W12">
-        <v>-0.01257785467128028</v>
+        <v>0.5553235908141962</v>
       </c>
       <c r="X12">
-        <v>0.04922238033500567</v>
+        <v>0.07939986118328243</v>
       </c>
       <c r="Y12">
-        <v>-0.06180023500628595</v>
-      </c>
-      <c r="Z12">
-        <v>0.1304347826086957</v>
-      </c>
-      <c r="AA12">
-        <v>-0.007234641788417533</v>
+        <v>0.4759237296309138</v>
       </c>
       <c r="AB12">
-        <v>0.04885797730067108</v>
-      </c>
-      <c r="AC12">
-        <v>-0.05609261908908861</v>
+        <v>0.07938129536023628</v>
       </c>
       <c r="AD12">
-        <v>1.08</v>
+        <v>1.86</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.08</v>
+        <v>1.86</v>
       </c>
       <c r="AG12">
-        <v>-1.09</v>
+        <v>-47.34</v>
       </c>
       <c r="AH12">
-        <v>0.01338621715418939</v>
+        <v>0.0006440086421804885</v>
       </c>
       <c r="AI12">
-        <v>0.01685393258426967</v>
+        <v>-0.04588061174148989</v>
       </c>
       <c r="AJ12">
-        <v>-0.01388358170933639</v>
+        <v>-0.01667512046664976</v>
       </c>
       <c r="AK12">
-        <v>-0.01760620255209175</v>
+        <v>0.5275239581011811</v>
       </c>
       <c r="AL12">
-        <v>0.035</v>
+        <v>104.4</v>
       </c>
       <c r="AM12">
-        <v>-2.015</v>
+        <v>-45.40000000000001</v>
       </c>
       <c r="AN12">
-        <v>-1.646341463414634</v>
+        <v>-0.1603448275862069</v>
       </c>
       <c r="AO12">
-        <v>-11.74285714285714</v>
+        <v>-0.1082375478927203</v>
       </c>
       <c r="AP12">
-        <v>1.661585365853658</v>
+        <v>4.081034482758621</v>
       </c>
       <c r="AQ12">
-        <v>0.2039702233250621</v>
+        <v>0.2488986784140969</v>
       </c>
     </row>
     <row r="13">
@@ -1957,7 +1918,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Brilliant Acquisition Corporation (NasdaqCM:BRLI)</t>
+          <t>Gushen, Inc. (OTCPK:GSHN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1965,8 +1926,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G13">
+        <v>-4.811320754716981</v>
+      </c>
+      <c r="H13">
+        <v>-4.811320754716981</v>
+      </c>
+      <c r="I13">
+        <v>-2.820754716981132</v>
+      </c>
+      <c r="J13">
+        <v>-2.820754716981132</v>
+      </c>
       <c r="K13">
-        <v>-0.443</v>
+        <v>-6.13</v>
+      </c>
+      <c r="L13">
+        <v>-2.891509433962264</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1990,64 +1966,61 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.504</v>
+        <v>1.09</v>
       </c>
       <c r="V13">
-        <v>0.008089887640449439</v>
+        <v>0.0001144188780651663</v>
       </c>
       <c r="W13">
-        <v>-0.0886</v>
+        <v>-4.609022556390977</v>
       </c>
       <c r="X13">
-        <v>0.04935442760262557</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y13">
-        <v>-0.1379544276026256</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>-0.08236367784622405</v>
+        <v>-4.688402804420394</v>
       </c>
       <c r="AB13">
-        <v>0.04885018094781638</v>
-      </c>
-      <c r="AC13">
-        <v>-0.1312138587940404</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AD13">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>0.6659999999999999</v>
+        <v>-1.09</v>
       </c>
       <c r="AH13">
-        <v>0.01843390578225933</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>1.010362694300518</v>
+        <v>-0</v>
       </c>
       <c r="AJ13">
-        <v>0.0105771368675158</v>
+        <v>-0.0001144319712429307</v>
       </c>
       <c r="AK13">
-        <v>1.018348623853211</v>
+        <v>0.1902268760907505</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-0.005</v>
+        <v>-0.006</v>
+      </c>
+      <c r="AN13">
+        <v>-0</v>
+      </c>
+      <c r="AP13">
+        <v>0.1844331641285956</v>
       </c>
       <c r="AQ13">
-        <v>72.2</v>
+        <v>996.6666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -2058,7 +2031,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Greencity Acquisition Corporation (NasdaqCM:GRCY)</t>
+          <t>Hainan Manaslu Acquisition Corp. (NasdaqGM:HMAC)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2067,7 +2040,7 @@
         </is>
       </c>
       <c r="K14">
-        <v>-0.66</v>
+        <v>-0.128</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2091,64 +2064,46 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0.135</v>
+        <v>0.15</v>
       </c>
       <c r="V14">
-        <v>0.002481617647058824</v>
-      </c>
-      <c r="W14">
-        <v>-0.132</v>
+        <v>0.001642935377875137</v>
       </c>
       <c r="X14">
-        <v>0.049248417318508</v>
-      </c>
-      <c r="Y14">
-        <v>-0.181248417318508</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>-0.1369136064529824</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AB14">
-        <v>0.04885643368130838</v>
-      </c>
-      <c r="AC14">
-        <v>-0.1857700401342908</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AD14">
-        <v>0.794</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0.794</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>0.659</v>
+        <v>-0.15</v>
       </c>
       <c r="AH14">
-        <v>0.01438562162553901</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>-0.781496062992126</v>
+        <v>-0</v>
       </c>
       <c r="AJ14">
-        <v>0.01196897873190578</v>
+        <v>-0.001645639056500274</v>
       </c>
       <c r="AK14">
-        <v>-0.5725456125108601</v>
+        <v>0.07075471698113207</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-0.012</v>
-      </c>
-      <c r="AQ14">
-        <v>53.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2159,7 +2114,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Puhui Wealth Investment Management Co., Ltd. (NasdaqCM:PHCF)</t>
+          <t>Greencity Acquisition Corporation (NasdaqCM:GRCY)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2167,26 +2122,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D15">
-        <v>-0.325</v>
-      </c>
-      <c r="G15">
-        <v>-1.798029556650246</v>
-      </c>
-      <c r="H15">
-        <v>-1.798029556650246</v>
-      </c>
-      <c r="I15">
-        <v>-1.763720359884852</v>
-      </c>
-      <c r="J15">
-        <v>-1.763720359884852</v>
-      </c>
       <c r="K15">
-        <v>-4.74</v>
-      </c>
-      <c r="L15">
-        <v>-2.334975369458129</v>
+        <v>0.57</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2195,7 +2132,7 @@
         <v>-0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2204,79 +2141,156 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0.581</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="V15">
-        <v>0.02934343434343434</v>
+        <v>0.0001612903225806452</v>
       </c>
       <c r="W15">
-        <v>-0.5530921820303384</v>
+        <v>-0.3149171270718232</v>
       </c>
       <c r="X15">
-        <v>0.05305845616230983</v>
+        <v>0.08080382931109441</v>
       </c>
       <c r="Y15">
-        <v>-0.6061506381926483</v>
-      </c>
-      <c r="Z15">
-        <v>0.2450873374227902</v>
-      </c>
-      <c r="AA15">
-        <v>-0.4322655269625438</v>
+        <v>-0.3957209563829176</v>
       </c>
       <c r="AB15">
-        <v>0.04947401342441458</v>
-      </c>
-      <c r="AC15">
-        <v>-0.4817395403869584</v>
+        <v>0.0790675157948539</v>
       </c>
       <c r="AD15">
-        <v>2.24</v>
+        <v>2.61</v>
       </c>
       <c r="AE15">
-        <v>1.026761652831249</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>3.266761652831249</v>
+        <v>2.61</v>
       </c>
       <c r="AG15">
-        <v>2.685761652831249</v>
+        <v>2.601</v>
       </c>
       <c r="AH15">
-        <v>0.1416220318221514</v>
+        <v>0.04468412942989215</v>
       </c>
       <c r="AI15">
-        <v>0.5005179944657789</v>
+        <v>-1.775510204081632</v>
       </c>
       <c r="AJ15">
-        <v>0.1194427697979747</v>
+        <v>0.04453690861457852</v>
       </c>
       <c r="AK15">
-        <v>0.4517102786238236</v>
+        <v>-1.758620689655172</v>
       </c>
       <c r="AL15">
-        <v>0.173</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>0.173</v>
-      </c>
-      <c r="AN15">
-        <v>-0.7237479806138934</v>
-      </c>
-      <c r="AO15">
-        <v>-22.71676300578035</v>
-      </c>
-      <c r="AP15">
-        <v>-0.8677743627887721</v>
+        <v>-0.24</v>
       </c>
       <c r="AQ15">
-        <v>-22.71676300578035</v>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SPK Acquisition Corp. (NasdaqGM:SPK)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K16">
+        <v>-0.802</v>
+      </c>
+      <c r="M16">
+        <v>41.1</v>
+      </c>
+      <c r="N16">
+        <v>1.568702290076336</v>
+      </c>
+      <c r="O16">
+        <v>-51.24688279301746</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>41.1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>0.038</v>
+      </c>
+      <c r="V16">
+        <v>0.001450381679389313</v>
+      </c>
+      <c r="W16">
+        <v>0.662809917355372</v>
+      </c>
+      <c r="X16">
+        <v>0.0794383304454899</v>
+      </c>
+      <c r="Y16">
+        <v>0.5833715869098821</v>
+      </c>
+      <c r="AB16">
+        <v>0.07936691711183226</v>
+      </c>
+      <c r="AD16">
+        <v>0.05</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0.05</v>
+      </c>
+      <c r="AG16">
+        <v>0.012</v>
+      </c>
+      <c r="AH16">
+        <v>0.001904761904761905</v>
+      </c>
+      <c r="AI16">
+        <v>-0.0228310502283105</v>
+      </c>
+      <c r="AJ16">
+        <v>0.0004578055852281399</v>
+      </c>
+      <c r="AK16">
+        <v>-0.005385996409335728</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-0.212</v>
+      </c>
+      <c r="AQ16">
+        <v>4.641509433962264</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/china/china_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.1233</v>
+        <v>-0.212</v>
       </c>
       <c r="E2">
-        <v>-0.01935</v>
-      </c>
-      <c r="F2">
-        <v>-0.03625</v>
+        <v>-0.05695</v>
       </c>
       <c r="G2">
-        <v>0.0466156867195058</v>
+        <v>0.08101893161064005</v>
       </c>
       <c r="H2">
-        <v>0.04649163465995312</v>
+        <v>0.08084897370921224</v>
       </c>
       <c r="I2">
-        <v>0.04803281782810115</v>
+        <v>0.06571568027603487</v>
       </c>
       <c r="J2">
-        <v>0.0441773025186598</v>
+        <v>0.05912468989147743</v>
       </c>
       <c r="K2">
-        <v>-899.7599999999999</v>
+        <v>-610.3830000000002</v>
       </c>
       <c r="L2">
-        <v>-0.08652486907218676</v>
+        <v>-0.1037394137472148</v>
       </c>
       <c r="M2">
-        <v>6690.896</v>
+        <v>2530.3915</v>
       </c>
       <c r="N2">
-        <v>0.2357432652165288</v>
+        <v>0.1408639637217293</v>
       </c>
       <c r="O2">
-        <v>-7.436311905396995</v>
+        <v>-4.145579906386645</v>
       </c>
       <c r="P2">
-        <v>1556.196</v>
+        <v>584.3915</v>
       </c>
       <c r="Q2">
-        <v>0.05483013431338662</v>
+        <v>0.03253239787411828</v>
       </c>
       <c r="R2">
-        <v>-1.729567884769272</v>
+        <v>-0.9574177196940279</v>
       </c>
       <c r="S2">
-        <v>5134.7</v>
+        <v>1946</v>
       </c>
       <c r="T2">
-        <v>0.7674159036398115</v>
+        <v>0.7690509551585198</v>
       </c>
       <c r="U2">
-        <v>2689.457</v>
+        <v>873.593</v>
       </c>
       <c r="V2">
-        <v>0.09475881478944675</v>
+        <v>0.04863191038207196</v>
       </c>
       <c r="W2">
-        <v>0.04656375002738439</v>
+        <v>0.03053717216282972</v>
       </c>
       <c r="X2">
-        <v>0.08012536483317503</v>
+        <v>0.07130244133056259</v>
       </c>
       <c r="Y2">
-        <v>-0.03356161480579065</v>
+        <v>-0.04076526916773286</v>
       </c>
       <c r="Z2">
-        <v>0.02865252739924236</v>
+        <v>0.01950887222132831</v>
       </c>
       <c r="AA2">
-        <v>-0.241900653985194</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07938024802941726</v>
+        <v>0.06756897650220572</v>
       </c>
       <c r="AC2">
-        <v>-0.323134811908714</v>
+        <v>-0.06754980635108339</v>
       </c>
       <c r="AD2">
-        <v>263748.66</v>
+        <v>246437.733</v>
       </c>
       <c r="AE2">
-        <v>0.9822600003606849</v>
+        <v>0.04711617531636255</v>
       </c>
       <c r="AF2">
-        <v>263749.6422600003</v>
+        <v>246437.7801161753</v>
       </c>
       <c r="AG2">
-        <v>261060.1852600003</v>
+        <v>245564.1871161753</v>
       </c>
       <c r="AH2">
-        <v>0.9028447683713786</v>
+        <v>0.932060166939111</v>
       </c>
       <c r="AI2">
-        <v>0.845209892900707</v>
+        <v>0.8513814627043756</v>
       </c>
       <c r="AJ2">
-        <v>0.9019420157190737</v>
+        <v>0.9318349466121264</v>
       </c>
       <c r="AK2">
-        <v>0.8438642192873825</v>
+        <v>0.8509315671174035</v>
       </c>
       <c r="AL2">
-        <v>156.891</v>
+        <v>73.75</v>
       </c>
       <c r="AM2">
-        <v>-0.8550000000000182</v>
+        <v>49.754</v>
       </c>
       <c r="AN2">
-        <v>522.9217546468401</v>
+        <v>634.0718547621437</v>
       </c>
       <c r="AO2">
-        <v>3.181367956096908</v>
+        <v>5.242277966101695</v>
       </c>
       <c r="AP2">
-        <v>517.5914453729871</v>
+        <v>631.8242652715498</v>
       </c>
       <c r="AQ2">
-        <v>-583.7754385964788</v>
+        <v>7.770591309241468</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yangzijiang Financial Holding Ltd. (SGX:YF8)</t>
+          <t>J-Yuan Trust Co., Ltd. (SHSE:600816)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,98 +721,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F3">
-        <v>0.011</v>
+      <c r="D3">
+        <v>-0.529</v>
+      </c>
+      <c r="E3">
+        <v>-0.221</v>
       </c>
       <c r="G3">
-        <v>1.171602787456446</v>
+        <v>-1.235294117647059</v>
       </c>
       <c r="H3">
-        <v>1.171602787456446</v>
+        <v>-1.235294117647059</v>
       </c>
       <c r="I3">
-        <v>0.9294425087108015</v>
+        <v>0.07720588235294118</v>
       </c>
       <c r="J3">
-        <v>0.7358885017421604</v>
+        <v>0.07720588235294118</v>
       </c>
       <c r="K3">
-        <v>192</v>
+        <v>34.2</v>
       </c>
       <c r="L3">
-        <v>0.8362369337979094</v>
+        <v>2.514705882352942</v>
       </c>
       <c r="M3">
-        <v>115.2</v>
+        <v>1.64</v>
       </c>
       <c r="N3">
-        <v>0.1178878428162096</v>
+        <v>0.0004115949303551261</v>
       </c>
       <c r="O3">
-        <v>0.6</v>
+        <v>0.047953216374269</v>
       </c>
       <c r="P3">
-        <v>51.1</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>0.05229226361031519</v>
+        <v>0.0004115949303551261</v>
       </c>
       <c r="R3">
-        <v>0.2661458333333334</v>
+        <v>0.047953216374269</v>
       </c>
       <c r="S3">
-        <v>64.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.5564236111111112</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>323.2</v>
+        <v>434.4</v>
       </c>
       <c r="V3">
-        <v>0.3307408923454768</v>
+        <v>0.1090224620404066</v>
+      </c>
+      <c r="W3">
+        <v>-0.2413549752999295</v>
       </c>
       <c r="X3">
-        <v>0.07938024802941726</v>
+        <v>0.06758262326480985</v>
+      </c>
+      <c r="Y3">
+        <v>-0.3089375985647393</v>
       </c>
       <c r="AB3">
-        <v>0.07938024802941726</v>
+        <v>0.06757880261636819</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.643</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.643</v>
       </c>
       <c r="AG3">
-        <v>-323.2</v>
+        <v>-433.757</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.0001613492916063489</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.0003449121171435269</v>
       </c>
       <c r="AJ3">
-        <v>-0.4941896024464832</v>
+        <v>-0.1221595029547337</v>
       </c>
       <c r="AK3">
-        <v>-0.1189065891615466</v>
+        <v>-0.3033598793713716</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-15.14</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.8149556400506971</v>
+      </c>
+      <c r="AO3">
+        <v>0.3125</v>
       </c>
       <c r="AP3">
-        <v>-1.508166122258516</v>
+        <v>-549.7553865652725</v>
+      </c>
+      <c r="AQ3">
+        <v>-0.06935270805812417</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hainan Haide Capital Management Co., Ltd. (SZSE:000567)</t>
+          <t>Wins Finance Holdings Inc. (OTCPK:WINS.F)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,121 +847,100 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.47</v>
-      </c>
-      <c r="E4">
-        <v>0.645</v>
+        <v>-0.351</v>
       </c>
       <c r="G4">
-        <v>0.5606975184439973</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.5606975184439973</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.8685446009389671</v>
+        <v>0.03655564408714188</v>
       </c>
       <c r="J4">
-        <v>0.7865153886280647</v>
+        <v>0.03655564408714188</v>
       </c>
       <c r="K4">
-        <v>97.8</v>
+        <v>-0.409</v>
       </c>
       <c r="L4">
-        <v>0.6559356136820925</v>
+        <v>-0.3684684684684684</v>
       </c>
       <c r="M4">
-        <v>56.4</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.03006076111288775</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.5766871165644172</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>56.4</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.03006076111288775</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.5766871165644172</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>18.3</v>
+        <v>0.115</v>
       </c>
       <c r="V4">
-        <v>0.009753757595139112</v>
+        <v>0.1008771929824561</v>
       </c>
       <c r="W4">
-        <v>0.1373402611992698</v>
+        <v>0.0774621212121212</v>
       </c>
       <c r="X4">
-        <v>0.08447386726560092</v>
+        <v>0.06958830605242705</v>
       </c>
       <c r="Y4">
-        <v>0.05286639393366883</v>
-      </c>
-      <c r="Z4">
-        <v>0.1701083856246434</v>
-      </c>
-      <c r="AA4">
-        <v>0.1337928630284592</v>
+        <v>0.007873815159694153</v>
       </c>
       <c r="AB4">
-        <v>0.07920480662503081</v>
-      </c>
-      <c r="AC4">
-        <v>0.05458805640342836</v>
+        <v>0.06757149508811579</v>
       </c>
       <c r="AD4">
-        <v>314</v>
+        <v>0.059</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.04711617531636255</v>
       </c>
       <c r="AF4">
-        <v>314</v>
+        <v>0.1061161753163626</v>
       </c>
       <c r="AG4">
-        <v>295.7</v>
+        <v>-0.008883824683637451</v>
       </c>
       <c r="AH4">
-        <v>0.1433659026572916</v>
+        <v>0.08515752978603452</v>
       </c>
       <c r="AI4">
-        <v>0.308903098868667</v>
+        <v>-0.02116446631530362</v>
       </c>
       <c r="AJ4">
-        <v>0.1361480731157051</v>
+        <v>-0.007854033809703702</v>
       </c>
       <c r="AK4">
-        <v>0.2962332197956321</v>
+        <v>0.001732116574932447</v>
       </c>
       <c r="AL4">
-        <v>19.4</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>19.4</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>2.42283950617284</v>
-      </c>
-      <c r="AO4">
-        <v>6.675257731958763</v>
+        <v>1.18</v>
       </c>
       <c r="AP4">
-        <v>2.281635802469136</v>
-      </c>
-      <c r="AQ4">
-        <v>6.675257731958763</v>
+        <v>-0.177676493672749</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shaanxi International Trust Co.,Ltd. (SZSE:000563)</t>
+          <t>Hainan Haide Capital Management Co., Ltd. (SZSE:000567)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,46 +960,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0862</v>
+        <v>0.309</v>
       </c>
       <c r="E5">
-        <v>0.0575</v>
+        <v>0.583</v>
       </c>
       <c r="G5">
-        <v>0.6256097560975609</v>
+        <v>0.7775133848899464</v>
       </c>
       <c r="H5">
-        <v>0.6208425720620842</v>
+        <v>0.7715645449137418</v>
       </c>
       <c r="I5">
-        <v>0.5698447893569843</v>
+        <v>0.8120166567519334</v>
       </c>
       <c r="J5">
-        <v>0.4252987940078956</v>
+        <v>0.726931929708306</v>
       </c>
       <c r="K5">
-        <v>107.1</v>
+        <v>126.9</v>
       </c>
       <c r="L5">
-        <v>0.3957871396895787</v>
+        <v>0.7549077929803689</v>
       </c>
       <c r="M5">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>0.01646933143416719</v>
+        <v>0.04948535233570863</v>
       </c>
       <c r="O5">
-        <v>0.3454715219421102</v>
+        <v>0.7880220646178092</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0.01646933143416719</v>
+        <v>0.04948535233570863</v>
       </c>
       <c r="R5">
-        <v>0.3454715219421102</v>
+        <v>0.7880220646178092</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,73 +1008,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>147.7</v>
+        <v>39.4</v>
       </c>
       <c r="V5">
-        <v>0.06574379061693225</v>
+        <v>0.0194972288202692</v>
       </c>
       <c r="W5">
-        <v>0.05701964542405366</v>
+        <v>0.1806405693950178</v>
       </c>
       <c r="X5">
-        <v>0.07944690035525567</v>
+        <v>0.07284598760861635</v>
       </c>
       <c r="Y5">
-        <v>-0.02242725493120201</v>
+        <v>0.1077945817864014</v>
       </c>
       <c r="Z5">
-        <v>0.1496424838661513</v>
+        <v>0.168403125626127</v>
       </c>
       <c r="AA5">
-        <v>0.06364276792062012</v>
+        <v>0.1224176090803108</v>
       </c>
       <c r="AB5">
-        <v>0.07936495446768028</v>
+        <v>0.0663138734669412</v>
       </c>
       <c r="AC5">
-        <v>-0.01572218654706016</v>
+        <v>0.05610373561336959</v>
       </c>
       <c r="AD5">
-        <v>4.92</v>
+        <v>493.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>4.92</v>
+        <v>493.1</v>
       </c>
       <c r="AG5">
-        <v>-142.78</v>
+        <v>453.7</v>
       </c>
       <c r="AH5">
-        <v>0.002185190449118818</v>
+        <v>0.1961494092843789</v>
       </c>
       <c r="AI5">
-        <v>0.002743973854167829</v>
+        <v>0.4004060089321965</v>
       </c>
       <c r="AJ5">
-        <v>-0.06786702284415969</v>
+        <v>0.1833501717518691</v>
       </c>
       <c r="AK5">
-        <v>-0.08677947147059539</v>
+        <v>0.380588876772083</v>
       </c>
       <c r="AL5">
-        <v>31.3</v>
+        <v>22.5</v>
       </c>
       <c r="AM5">
-        <v>31.3</v>
+        <v>22.38</v>
       </c>
       <c r="AN5">
-        <v>0.03186528497409327</v>
+        <v>3.609809663250366</v>
       </c>
       <c r="AO5">
-        <v>4.926517571884983</v>
+        <v>6.066666666666666</v>
       </c>
       <c r="AP5">
-        <v>-0.924740932642487</v>
+        <v>3.321376281112738</v>
       </c>
       <c r="AQ5">
-        <v>4.926517571884983</v>
+        <v>6.099195710455764</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kunwu Jiuding Investment Holdings Co., Ltd. (SHSE:600053)</t>
+          <t>Shaanxi International Trust Co.,Ltd. (SZSE:000563)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,46 +1094,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.171</v>
+        <v>0.21</v>
       </c>
       <c r="E6">
-        <v>-0.264</v>
+        <v>0.429</v>
       </c>
       <c r="G6">
-        <v>-0.03512605042016807</v>
+        <v>0.5232827373295601</v>
       </c>
       <c r="H6">
-        <v>-0.03512605042016807</v>
+        <v>0.5232827373295601</v>
       </c>
       <c r="I6">
-        <v>0.4369747899159664</v>
+        <v>0.6246462567532802</v>
       </c>
       <c r="J6">
-        <v>0.3378830320006791</v>
+        <v>0.4738018752114981</v>
       </c>
       <c r="K6">
-        <v>15.4</v>
+        <v>144.8</v>
       </c>
       <c r="L6">
-        <v>0.2588235294117647</v>
+        <v>0.3725237972729612</v>
       </c>
       <c r="M6">
-        <v>0.893</v>
+        <v>35.3</v>
       </c>
       <c r="N6">
-        <v>0.000961248654467169</v>
+        <v>0.01610034207525655</v>
       </c>
       <c r="O6">
-        <v>0.05798701298701299</v>
+        <v>0.2437845303867403</v>
       </c>
       <c r="P6">
-        <v>0.893</v>
+        <v>35.3</v>
       </c>
       <c r="Q6">
-        <v>0.000961248654467169</v>
+        <v>0.01610034207525655</v>
       </c>
       <c r="R6">
-        <v>0.05798701298701299</v>
+        <v>0.2437845303867403</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1151,73 +1142,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>35.5</v>
+        <v>175.5</v>
       </c>
       <c r="V6">
-        <v>0.03821313240043057</v>
+        <v>0.08004561003420753</v>
       </c>
       <c r="W6">
-        <v>0.03610785463071512</v>
+        <v>0.0809798109725407</v>
       </c>
       <c r="X6">
-        <v>0.07938024802941726</v>
+        <v>0.06761320250817783</v>
       </c>
       <c r="Y6">
-        <v>-0.04327239339870214</v>
+        <v>0.01336660846436287</v>
       </c>
       <c r="Z6">
-        <v>0.1349686849966995</v>
+        <v>0.2362458366761481</v>
       </c>
       <c r="AA6">
-        <v>0.04560362851182939</v>
+        <v>0.1119337204280683</v>
       </c>
       <c r="AB6">
-        <v>0.07938024802941726</v>
+        <v>0.06756897650220572</v>
       </c>
       <c r="AC6">
-        <v>-0.03377661951758787</v>
+        <v>0.04436474392586255</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AG6">
-        <v>-35.5</v>
+        <v>-172.04</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.001575620685258383</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.001491919488090516</v>
       </c>
       <c r="AJ6">
-        <v>-0.03973139339675433</v>
+        <v>-0.08514892648208823</v>
       </c>
       <c r="AK6">
-        <v>-0.09494517250601765</v>
+        <v>-0.08025526436095276</v>
       </c>
       <c r="AL6">
-        <v>0.861</v>
+        <v>35.2</v>
       </c>
       <c r="AM6">
-        <v>-6.559</v>
+        <v>35.2</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>0.01421528348397699</v>
       </c>
       <c r="AO6">
-        <v>30.19744483159117</v>
+        <v>6.897727272727272</v>
       </c>
       <c r="AP6">
-        <v>-1.349809885931559</v>
+        <v>-0.7068200493015612</v>
       </c>
       <c r="AQ6">
-        <v>-3.964018905320933</v>
+        <v>6.897727272727272</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shandong International Trust Co., Ltd. (SEHK:1697)</t>
+          <t>Kunwu Jiuding Investment Holdings Co., Ltd. (SHSE:600053)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1236,86 +1227,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.21</v>
+      </c>
+      <c r="E7">
+        <v>-0.15</v>
+      </c>
+      <c r="G7">
+        <v>0.8073878627968338</v>
+      </c>
+      <c r="H7">
+        <v>0.8073878627968338</v>
+      </c>
+      <c r="I7">
+        <v>0.2482849604221636</v>
+      </c>
+      <c r="J7">
+        <v>0.2337282534683803</v>
+      </c>
       <c r="K7">
-        <v>-60.7</v>
+        <v>11.3</v>
+      </c>
+      <c r="L7">
+        <v>0.2981530343007916</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>11.4</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.01319597175599028</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.008849557522124</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>11.4</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.01319597175599028</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.008849557522124</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>27.8</v>
+        <v>39.8</v>
       </c>
       <c r="V7">
-        <v>0.1192621192621193</v>
+        <v>0.04607014700775552</v>
       </c>
       <c r="W7">
-        <v>-0.03703025866276232</v>
+        <v>0.02648851383028598</v>
       </c>
       <c r="X7">
-        <v>0.1197385320252116</v>
+        <v>0.0676298591943077</v>
       </c>
       <c r="Y7">
-        <v>-0.1567687906879739</v>
+        <v>-0.04114134536402171</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>0.09631879233007611</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.02251242310749231</v>
       </c>
       <c r="AB7">
-        <v>0.07868261712126562</v>
+        <v>0.06757423692024914</v>
       </c>
       <c r="AC7">
-        <v>-0.07868261712126562</v>
+        <v>-0.04506181381275683</v>
       </c>
       <c r="AD7">
-        <v>309.1</v>
+        <v>2.03</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>309.1</v>
+        <v>2.03</v>
       </c>
       <c r="AG7">
-        <v>281.3</v>
+        <v>-37.77</v>
       </c>
       <c r="AH7">
-        <v>0.5700848395426042</v>
+        <v>0.002344300347603155</v>
       </c>
       <c r="AI7">
-        <v>0.1691196585872955</v>
+        <v>0.005028112847695242</v>
       </c>
       <c r="AJ7">
-        <v>0.5468506998444791</v>
+        <v>-0.04571919673659109</v>
       </c>
       <c r="AK7">
-        <v>0.1562864603589088</v>
+        <v>-0.1037836946665567</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>-0.8299999999999998</v>
+      </c>
+      <c r="AN7">
+        <v>0.211018711018711</v>
+      </c>
+      <c r="AO7">
+        <v>6.315436241610739</v>
+      </c>
+      <c r="AP7">
+        <v>-3.926195426195426</v>
+      </c>
+      <c r="AQ7">
+        <v>-11.33734939759036</v>
       </c>
     </row>
     <row r="8">
@@ -1335,13 +1362,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0756</v>
+        <v>-0.212</v>
       </c>
       <c r="E8">
-        <v>-0.09619999999999999</v>
-      </c>
-      <c r="F8">
-        <v>-0.08349999999999999</v>
+        <v>-0.199</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1356,85 +1380,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>1475.2</v>
+        <v>809.8</v>
       </c>
       <c r="L8">
-        <v>0.2011398652886477</v>
+        <v>0.3104228159619734</v>
       </c>
       <c r="M8">
-        <v>3619.903</v>
+        <v>1412.1515</v>
       </c>
       <c r="N8">
-        <v>0.6847835874541258</v>
+        <v>0.3705753536095731</v>
       </c>
       <c r="O8">
-        <v>2.453838801518438</v>
+        <v>1.743827488268708</v>
       </c>
       <c r="P8">
-        <v>534.303</v>
+        <v>267.1515</v>
       </c>
       <c r="Q8">
-        <v>0.101075063372555</v>
+        <v>0.07010562363870156</v>
       </c>
       <c r="R8">
-        <v>0.3621902114967462</v>
+        <v>0.3298981229933317</v>
       </c>
       <c r="S8">
-        <v>3085.6</v>
+        <v>1145</v>
       </c>
       <c r="T8">
-        <v>0.8523985311208615</v>
+        <v>0.8108195190105312</v>
       </c>
       <c r="U8">
-        <v>2054.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="V8">
-        <v>0.3886156407249064</v>
+        <v>0.02128217912719448</v>
       </c>
       <c r="W8">
-        <v>0.06285765417211714</v>
+        <v>0.03053717216282972</v>
       </c>
       <c r="X8">
-        <v>0.8688941451403585</v>
+        <v>0.8033894472981138</v>
       </c>
       <c r="Y8">
-        <v>-0.8060364909682414</v>
+        <v>-0.7728522751352841</v>
       </c>
       <c r="Z8">
-        <v>0.04160686386746074</v>
+        <v>0.01631786783696769</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0795740455441699</v>
+        <v>0.06651920755038396</v>
       </c>
       <c r="AC8">
-        <v>-0.0795740455441699</v>
+        <v>-0.06651920755038396</v>
       </c>
       <c r="AD8">
-        <v>137128.4</v>
+        <v>129906.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>137128.4</v>
+        <v>129906.7</v>
       </c>
       <c r="AG8">
-        <v>135074.1</v>
+        <v>129825.6</v>
       </c>
       <c r="AH8">
-        <v>0.9628816146659119</v>
+        <v>0.9715018389528962</v>
       </c>
       <c r="AI8">
-        <v>0.8154754825235374</v>
+        <v>0.813521036794429</v>
       </c>
       <c r="AJ8">
-        <v>0.9623383535087913</v>
+        <v>0.9714845442443408</v>
       </c>
       <c r="AK8">
-        <v>0.8131933561825683</v>
+        <v>0.813426280392523</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1451,7 +1475,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>China Huarong Asset Management Co., Ltd. (SEHK:2799)</t>
+          <t>Shandong International Trust Co., Ltd. (SEHK:1697)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1460,7 +1484,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.239</v>
+        <v>0.115</v>
+      </c>
+      <c r="E9">
+        <v>0.0361</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1475,85 +1502,82 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>-2633.1</v>
+        <v>128.2</v>
       </c>
       <c r="L9">
-        <v>-1.135593220338983</v>
+        <v>0.4590046544933762</v>
       </c>
       <c r="M9">
-        <v>2803.1</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.664304673428761</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>-1.064562682769359</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>876.5</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.2077211110057825</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0.332877596749079</v>
+        <v>-0</v>
       </c>
       <c r="S9">
-        <v>1926.6</v>
-      </c>
-      <c r="T9">
-        <v>0.6873104776854198</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>0.018</v>
+        <v>34.5</v>
       </c>
       <c r="V9">
-        <v>4.265807185515214e-06</v>
+        <v>0.1606893339543549</v>
       </c>
       <c r="W9">
-        <v>-0.3803408926765853</v>
+        <v>0.08441986039773475</v>
       </c>
       <c r="X9">
-        <v>0.9880619788468232</v>
+        <v>0.07805463983759377</v>
       </c>
       <c r="Y9">
-        <v>-1.368402871523408</v>
+        <v>0.00636522056014098</v>
       </c>
       <c r="Z9">
-        <v>0.01275064668825227</v>
+        <v>0.1551752875159731</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.08247776862382139</v>
+        <v>0.06754980635108339</v>
       </c>
       <c r="AC9">
-        <v>-0.08247776862382139</v>
+        <v>-0.06754980635108339</v>
       </c>
       <c r="AD9">
-        <v>125981.6</v>
+        <v>104.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>125981.6</v>
+        <v>104.2</v>
       </c>
       <c r="AG9">
-        <v>125981.582</v>
+        <v>69.7</v>
       </c>
       <c r="AH9">
-        <v>0.9675916965435034</v>
+        <v>0.3267481969269364</v>
       </c>
       <c r="AI9">
-        <v>0.9273465109380302</v>
+        <v>0.06368803862844569</v>
       </c>
       <c r="AJ9">
-        <v>0.9675916920631334</v>
+        <v>0.2450773558368495</v>
       </c>
       <c r="AK9">
-        <v>0.927346501311629</v>
+        <v>0.04351898101898102</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1570,7 +1594,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Puhui Wealth Investment Management Co., Ltd. (NasdaqCM:PHCF)</t>
+          <t>Tian Tu Capital Co., Ltd. (SEHK:1973)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1578,113 +1602,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D10">
+        <v>-0.338</v>
+      </c>
       <c r="G10">
-        <v>-1.495901639344262</v>
+        <v>8.644295302013424</v>
       </c>
       <c r="H10">
-        <v>-1.495901639344262</v>
+        <v>8.644295302013424</v>
       </c>
       <c r="I10">
-        <v>-1.275185245931204</v>
+        <v>-0.07449664429530202</v>
       </c>
       <c r="J10">
-        <v>-1.275185245931204</v>
+        <v>-0.07449664429530202</v>
       </c>
       <c r="K10">
-        <v>-5.66</v>
+        <v>-7.52</v>
       </c>
       <c r="L10">
-        <v>-2.319672131147541</v>
+        <v>-0.5046979865771811</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>25.5</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.04374678332475553</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-3.390957446808511</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>25.5</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.04374678332475553</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>-3.390957446808511</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>0.952</v>
+        <v>63.8</v>
       </c>
       <c r="V10">
-        <v>0.15787728026534</v>
+        <v>0.109452736318408</v>
       </c>
       <c r="W10">
-        <v>-0.9085072231139647</v>
+        <v>-0.007128637785572091</v>
       </c>
       <c r="X10">
-        <v>0.09766286111917769</v>
+        <v>0.07324831963285955</v>
       </c>
       <c r="Y10">
-        <v>-1.006170084233142</v>
+        <v>-0.08037695741843164</v>
       </c>
       <c r="Z10">
-        <v>0.3793968833266199</v>
+        <v>0.01178711676048895</v>
       </c>
       <c r="AA10">
-        <v>-0.483801307970388</v>
+        <v>-0.000878100644573338</v>
       </c>
       <c r="AB10">
-        <v>0.07999054722321847</v>
+        <v>0.06756046547474071</v>
       </c>
       <c r="AC10">
-        <v>-0.5637918551936065</v>
+        <v>-0.06843856611931404</v>
       </c>
       <c r="AD10">
-        <v>2.64</v>
+        <v>153.1</v>
       </c>
       <c r="AE10">
-        <v>0.9822600003606849</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>3.622260000360685</v>
+        <v>153.1</v>
       </c>
       <c r="AG10">
-        <v>2.670260000360685</v>
+        <v>89.3</v>
       </c>
       <c r="AH10">
-        <v>0.3752758421577256</v>
+        <v>0.2080163043478261</v>
       </c>
       <c r="AI10">
-        <v>0.5738451838412403</v>
+        <v>0.1349612129760226</v>
       </c>
       <c r="AJ10">
-        <v>0.3069172645702524</v>
+        <v>0.1328473668551026</v>
       </c>
       <c r="AK10">
-        <v>0.4981586714414985</v>
+        <v>0.08341117130580983</v>
       </c>
       <c r="AL10">
-        <v>0.93</v>
+        <v>11.2</v>
       </c>
       <c r="AM10">
-        <v>0.928</v>
+        <v>10.663</v>
       </c>
       <c r="AN10">
-        <v>-0.9723756906077349</v>
+        <v>-85.05555555555556</v>
       </c>
       <c r="AO10">
-        <v>-3.731182795698925</v>
+        <v>-0.09910714285714287</v>
       </c>
       <c r="AP10">
-        <v>-0.9835211787700499</v>
+        <v>-49.61111111111111</v>
       </c>
       <c r="AQ10">
-        <v>-3.739224137931035</v>
+        <v>-0.1040982837850511</v>
       </c>
     </row>
     <row r="11">
@@ -1695,7 +1725,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Brilliant Acquisition Corporation (NasdaqCM:BRLI)</t>
+          <t>China Huarong Asset Management Co., Ltd. (SEHK:2799)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1703,92 +1733,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D11">
+        <v>-0.218</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
       <c r="K11">
-        <v>-1.51</v>
+        <v>-1858.9</v>
+      </c>
+      <c r="L11">
+        <v>-0.7838498840396374</v>
       </c>
       <c r="M11">
-        <v>17.3</v>
+        <v>881.1</v>
       </c>
       <c r="N11">
-        <v>0.7792792792792793</v>
+        <v>0.2144317352153809</v>
       </c>
       <c r="O11">
-        <v>-11.45695364238411</v>
+        <v>-0.4739899940825219</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>143.4</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.03489900219031394</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>-0.07714239604066921</v>
       </c>
       <c r="S11">
-        <v>17.3</v>
+        <v>737.7</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0.8372488934286687</v>
       </c>
       <c r="U11">
-        <v>31.2</v>
+        <v>0.012</v>
       </c>
       <c r="V11">
-        <v>1.405405405405405</v>
+        <v>2.920418593331711e-06</v>
       </c>
       <c r="W11">
-        <v>125.8333333333333</v>
+        <v>-0.1918072537790848</v>
       </c>
       <c r="X11">
-        <v>0.08415116908152444</v>
+        <v>0.6756995646667512</v>
       </c>
       <c r="Y11">
-        <v>125.7491821642518</v>
+        <v>-0.867506818445836</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>0.01748538140272972</v>
       </c>
       <c r="AA11">
-        <v>-2.308868501529052</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07843182176665267</v>
+        <v>0.06846878856552871</v>
       </c>
       <c r="AC11">
-        <v>-2.387300323295705</v>
+        <v>-0.06846878856552871</v>
       </c>
       <c r="AD11">
-        <v>3.48</v>
+        <v>115767.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>3.48</v>
+        <v>115767.5</v>
       </c>
       <c r="AG11">
-        <v>-27.72</v>
+        <v>115767.488</v>
       </c>
       <c r="AH11">
-        <v>0.1355140186915888</v>
+        <v>0.9657230566457979</v>
       </c>
       <c r="AI11">
-        <v>-7.25</v>
+        <v>0.9552601504255732</v>
       </c>
       <c r="AJ11">
-        <v>5.021739130434783</v>
+        <v>0.965723053214572</v>
       </c>
       <c r="AK11">
-        <v>0.875</v>
+        <v>0.9552601459955009</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-0.066</v>
-      </c>
-      <c r="AQ11">
-        <v>22.87878787878788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1799,7 +1844,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anxin Trust Co., Ltd (SHSE:600816)</t>
+          <t>Distoken Acquisition Corporation (NasdaqGM:DIST)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1807,26 +1852,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D12">
-        <v>-0.471</v>
-      </c>
-      <c r="G12">
-        <v>-0.6503067484662576</v>
-      </c>
-      <c r="H12">
-        <v>-0.6503067484662576</v>
-      </c>
-      <c r="I12">
-        <v>-0.3466257668711656</v>
-      </c>
-      <c r="J12">
-        <v>-0.3466257668711656</v>
-      </c>
       <c r="K12">
-        <v>-79.8</v>
-      </c>
-      <c r="L12">
-        <v>-2.447852760736196</v>
+        <v>1.08</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1835,7 +1862,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1844,70 +1871,70 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>49.2</v>
+        <v>0.349</v>
       </c>
       <c r="V12">
-        <v>0.01704604510965596</v>
+        <v>0.005117302052785923</v>
       </c>
       <c r="W12">
-        <v>0.5553235908141962</v>
+        <v>63.52941176470588</v>
       </c>
       <c r="X12">
-        <v>0.07939986118328243</v>
+        <v>0.06757945656854644</v>
       </c>
       <c r="Y12">
-        <v>0.4759237296309138</v>
+        <v>63.46183230813734</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>-1.581939799331104</v>
       </c>
       <c r="AB12">
-        <v>0.07938129536023628</v>
+        <v>0.06757913876607612</v>
+      </c>
+      <c r="AC12">
+        <v>-1.64951893809718</v>
       </c>
       <c r="AD12">
-        <v>1.86</v>
+        <v>0.001</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.86</v>
+        <v>0.001</v>
       </c>
       <c r="AG12">
-        <v>-47.34</v>
+        <v>-0.348</v>
       </c>
       <c r="AH12">
-        <v>0.0006440086421804885</v>
+        <v>1.46625416049618e-05</v>
       </c>
       <c r="AI12">
-        <v>-0.04588061174148989</v>
+        <v>0.002583979328165375</v>
       </c>
       <c r="AJ12">
-        <v>-0.01667512046664976</v>
+        <v>-0.005128809762424098</v>
       </c>
       <c r="AK12">
-        <v>0.5275239581011811</v>
+        <v>-9.157894736842097</v>
       </c>
       <c r="AL12">
-        <v>104.4</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>-45.40000000000001</v>
-      </c>
-      <c r="AN12">
-        <v>-0.1603448275862069</v>
-      </c>
-      <c r="AO12">
-        <v>-0.1082375478927203</v>
-      </c>
-      <c r="AP12">
-        <v>4.081034482758621</v>
+        <v>-2.14</v>
       </c>
       <c r="AQ12">
-        <v>0.2488986784140969</v>
+        <v>0.3392523364485981</v>
       </c>
     </row>
     <row r="13">
@@ -1918,7 +1945,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gushen, Inc. (OTCPK:GSHN)</t>
+          <t>Global Lights Acquisition Corp (NasdaqGM:GLAC)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1926,23 +1953,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G13">
-        <v>-4.811320754716981</v>
-      </c>
-      <c r="H13">
-        <v>-4.811320754716981</v>
-      </c>
-      <c r="I13">
-        <v>-2.820754716981132</v>
-      </c>
-      <c r="J13">
-        <v>-2.820754716981132</v>
-      </c>
       <c r="K13">
-        <v>-6.13</v>
-      </c>
-      <c r="L13">
-        <v>-2.891509433962264</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1966,22 +1978,16 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>0.0001144188780651663</v>
-      </c>
-      <c r="W13">
-        <v>-4.609022556390977</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>0.07938024802941726</v>
-      </c>
-      <c r="Y13">
-        <v>-4.688402804420394</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="AB13">
-        <v>0.07938024802941726</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -1993,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>-1.09</v>
+        <v>0</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -2002,25 +2008,16 @@
         <v>-0</v>
       </c>
       <c r="AJ13">
-        <v>-0.0001144319712429307</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>0.1902268760907505</v>
+        <v>-0</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-0.006</v>
-      </c>
-      <c r="AN13">
-        <v>-0</v>
-      </c>
-      <c r="AP13">
-        <v>0.1844331641285956</v>
-      </c>
-      <c r="AQ13">
-        <v>996.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2031,7 +2028,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hainan Manaslu Acquisition Corp. (NasdaqGM:HMAC)</t>
+          <t>Greencity Acquisition Corporation (OTCPK:GRCY.F)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2040,16 +2037,16 @@
         </is>
       </c>
       <c r="K14">
-        <v>-0.128</v>
+        <v>0.612</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>36.4</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>2.275</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>59.47712418300654</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -2058,52 +2055,64 @@
         <v>-0</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>36.4</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>0.15</v>
+        <v>0.007</v>
       </c>
       <c r="V14">
-        <v>0.001642935377875137</v>
+        <v>0.0004375</v>
+      </c>
+      <c r="W14">
+        <v>-0.1871559633027523</v>
       </c>
       <c r="X14">
-        <v>0.07938024802941726</v>
+        <v>0.07130244133056259</v>
+      </c>
+      <c r="Y14">
+        <v>-0.2584584046333149</v>
       </c>
       <c r="AB14">
-        <v>0.07938024802941726</v>
+        <v>0.06756593228623112</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AG14">
-        <v>-0.15</v>
+        <v>2.753</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.1471215351812367</v>
       </c>
       <c r="AI14">
-        <v>-0</v>
+        <v>-1.827814569536424</v>
       </c>
       <c r="AJ14">
-        <v>-0.001645639056500274</v>
+        <v>0.1468031781581614</v>
       </c>
       <c r="AK14">
-        <v>0.07075471698113207</v>
+        <v>-1.814765985497693</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>-0.379</v>
+      </c>
+      <c r="AQ14">
+        <v>1.725593667546174</v>
       </c>
     </row>
     <row r="15">
@@ -2114,7 +2123,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Greencity Acquisition Corporation (NasdaqCM:GRCY)</t>
+          <t>Brilliant Acquisition Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2123,16 +2132,16 @@
         </is>
       </c>
       <c r="K15">
-        <v>0.57</v>
+        <v>-0.362</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>26.9</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>3.153575615474795</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>-74.30939226519337</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2141,156 +2150,61 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>26.9</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
       </c>
       <c r="U15">
-        <v>0.008999999999999999</v>
+        <v>4.61</v>
       </c>
       <c r="V15">
-        <v>0.0001612903225806452</v>
+        <v>0.5404454865181713</v>
       </c>
       <c r="W15">
-        <v>-0.3149171270718232</v>
+        <v>0.09141414141414141</v>
       </c>
       <c r="X15">
-        <v>0.08080382931109441</v>
+        <v>0.07815623318419901</v>
       </c>
       <c r="Y15">
-        <v>-0.3957209563829176</v>
+        <v>0.0132579082299424</v>
       </c>
       <c r="AB15">
-        <v>0.0790675157948539</v>
+        <v>0.06754961542673983</v>
       </c>
       <c r="AD15">
-        <v>2.61</v>
+        <v>4.18</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>2.61</v>
+        <v>4.18</v>
       </c>
       <c r="AG15">
-        <v>2.601</v>
+        <v>-0.4300000000000006</v>
       </c>
       <c r="AH15">
-        <v>0.04468412942989215</v>
+        <v>0.3288749016522423</v>
       </c>
       <c r="AI15">
-        <v>-1.775510204081632</v>
+        <v>-8.530612244897956</v>
       </c>
       <c r="AJ15">
-        <v>0.04453690861457852</v>
+        <v>-0.05308641975308651</v>
       </c>
       <c r="AK15">
-        <v>-1.758620689655172</v>
+        <v>0.08431372549019618</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-0.24</v>
-      </c>
-      <c r="AQ15">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SPK Acquisition Corp. (NasdaqGM:SPK)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K16">
-        <v>-0.802</v>
-      </c>
-      <c r="M16">
-        <v>41.1</v>
-      </c>
-      <c r="N16">
-        <v>1.568702290076336</v>
-      </c>
-      <c r="O16">
-        <v>-51.24688279301746</v>
-      </c>
-      <c r="P16">
-        <v>-0</v>
-      </c>
-      <c r="Q16">
-        <v>-0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>41.1</v>
-      </c>
-      <c r="T16">
-        <v>1</v>
-      </c>
-      <c r="U16">
-        <v>0.038</v>
-      </c>
-      <c r="V16">
-        <v>0.001450381679389313</v>
-      </c>
-      <c r="W16">
-        <v>0.662809917355372</v>
-      </c>
-      <c r="X16">
-        <v>0.0794383304454899</v>
-      </c>
-      <c r="Y16">
-        <v>0.5833715869098821</v>
-      </c>
-      <c r="AB16">
-        <v>0.07936691711183226</v>
-      </c>
-      <c r="AD16">
-        <v>0.05</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0.05</v>
-      </c>
-      <c r="AG16">
-        <v>0.012</v>
-      </c>
-      <c r="AH16">
-        <v>0.001904761904761905</v>
-      </c>
-      <c r="AI16">
-        <v>-0.0228310502283105</v>
-      </c>
-      <c r="AJ16">
-        <v>0.0004578055852281399</v>
-      </c>
-      <c r="AK16">
-        <v>-0.005385996409335728</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-0.212</v>
-      </c>
-      <c r="AQ16">
-        <v>4.641509433962264</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/china/china_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,109 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.16385</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="E2">
-        <v>0.011</v>
+        <v>-0.0165</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.06430585503400232</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.06409760232948158</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.05265660419085531</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.04347524118114172</v>
       </c>
       <c r="K2">
-        <v>2188.4</v>
+        <v>2280.404</v>
       </c>
       <c r="L2">
-        <v>0.4799438559554357</v>
+        <v>0.4202657525662999</v>
       </c>
       <c r="M2">
-        <v>358.287</v>
+        <v>570.667</v>
       </c>
       <c r="N2">
-        <v>0.02765584475731753</v>
+        <v>0.02440969771629731</v>
       </c>
       <c r="O2">
-        <v>0.1637209833668434</v>
+        <v>0.2502482016344472</v>
       </c>
       <c r="P2">
-        <v>358.287</v>
+        <v>550.967</v>
       </c>
       <c r="Q2">
-        <v>0.02765584475731753</v>
+        <v>0.02356705034924953</v>
       </c>
       <c r="R2">
-        <v>0.1637209833668434</v>
+        <v>0.2416093814955595</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>19.7</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.03452100787324307</v>
       </c>
       <c r="U2">
-        <v>76.41000000000001</v>
+        <v>541.11</v>
       </c>
       <c r="V2">
-        <v>0.00589801778436458</v>
+        <v>0.02314542724787948</v>
       </c>
       <c r="W2">
-        <v>0.1565322078283891</v>
+        <v>0.0176658626730392</v>
       </c>
       <c r="X2">
-        <v>0.4505315600945394</v>
+        <v>0.07903445605113522</v>
       </c>
       <c r="Y2">
-        <v>-0.2939993522661504</v>
+        <v>-0.06136859337809603</v>
       </c>
       <c r="Z2">
-        <v>0.01661414417692884</v>
+        <v>0.01923238623681656</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.0008563086080071875</v>
       </c>
       <c r="AB2">
-        <v>0.0692139059586343</v>
+        <v>0.07163787514990733</v>
       </c>
       <c r="AC2">
-        <v>-0.0692139059586343</v>
+        <v>-0.06920482969145315</v>
       </c>
       <c r="AD2">
-        <v>241642.3</v>
+        <v>242383.841</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>241642.3</v>
+        <v>242383.841</v>
       </c>
       <c r="AG2">
-        <v>241565.89</v>
+        <v>241842.731</v>
       </c>
       <c r="AH2">
-        <v>0.9491149755987391</v>
+        <v>0.9120316207392072</v>
       </c>
       <c r="AI2">
-        <v>0.8665036280280631</v>
+        <v>0.8421666200079656</v>
       </c>
       <c r="AJ2">
-        <v>0.9490996993608662</v>
+        <v>0.9118521459150108</v>
       </c>
       <c r="AK2">
-        <v>0.8664670402446479</v>
+        <v>0.8418693192194315</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>118.91</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>86.31</v>
+      </c>
+      <c r="AN2">
+        <v>846.4009533121487</v>
+      </c>
+      <c r="AO2">
+        <v>2.40282566647044</v>
+      </c>
+      <c r="AP2">
+        <v>844.5114048259246</v>
+      </c>
+      <c r="AQ2">
+        <v>3.310392770246785</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>China Cinda Asset Management Co., Ltd. (SEHK:1359)</t>
+          <t>Shaanxi International Trust Co.,Ltd. (SZSE:000563)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0727</v>
+        <v>0.148</v>
       </c>
       <c r="E3">
-        <v>-0.202</v>
+        <v>0.169</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.6008179959100205</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.6008179959100205</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.6965235173824131</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.5247226676444674</v>
       </c>
       <c r="K3">
-        <v>537.9</v>
+        <v>168.9</v>
       </c>
       <c r="L3">
-        <v>0.1626598929511022</v>
+        <v>0.345398773006135</v>
       </c>
       <c r="M3">
-        <v>228.987</v>
+        <v>62.5</v>
       </c>
       <c r="N3">
-        <v>0.03669663461538462</v>
+        <v>0.02505813487290514</v>
       </c>
       <c r="O3">
-        <v>0.4257055214723927</v>
+        <v>0.3700414446417999</v>
       </c>
       <c r="P3">
-        <v>228.987</v>
+        <v>62.5</v>
       </c>
       <c r="Q3">
-        <v>0.03669663461538462</v>
+        <v>0.02505813487290514</v>
       </c>
       <c r="R3">
-        <v>0.4257055214723927</v>
+        <v>0.3700414446417999</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,61 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>76.40000000000001</v>
+        <v>184.1</v>
       </c>
       <c r="V3">
-        <v>0.01224358974358974</v>
+        <v>0.07381124208162938</v>
       </c>
       <c r="W3">
-        <v>0.02149270191112834</v>
+        <v>0.07293690892602669</v>
       </c>
       <c r="X3">
-        <v>0.470667497826149</v>
+        <v>0.07275762436867722</v>
       </c>
       <c r="Y3">
-        <v>-0.4491747959150207</v>
+        <v>0.0001792845573494739</v>
       </c>
       <c r="Z3">
-        <v>0.0216107310621012</v>
+        <v>0.2281145330882696</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.1196968663305489</v>
       </c>
       <c r="AB3">
-        <v>0.06799423374027234</v>
+        <v>0.07273561037440437</v>
       </c>
       <c r="AC3">
-        <v>-0.06799423374027234</v>
+        <v>0.04696125595614457</v>
       </c>
       <c r="AD3">
-        <v>122833.2</v>
+        <v>2.11</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>122833.2</v>
+        <v>2.11</v>
       </c>
       <c r="AG3">
-        <v>122756.8</v>
+        <v>-181.99</v>
       </c>
       <c r="AH3">
-        <v>0.9516553397606939</v>
+        <v>0.0008452475854361037</v>
       </c>
       <c r="AI3">
-        <v>0.8038369568204931</v>
+        <v>0.0008395637451705189</v>
       </c>
       <c r="AJ3">
-        <v>0.9516267070190888</v>
+        <v>-0.07870824881823017</v>
       </c>
       <c r="AK3">
-        <v>0.8037388317591182</v>
+        <v>-0.07813714251366401</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>73.5</v>
+      </c>
+      <c r="AN3">
+        <v>0.006184056271981242</v>
+      </c>
+      <c r="AO3">
+        <v>4.634013605442177</v>
+      </c>
+      <c r="AP3">
+        <v>-0.5333821805392731</v>
+      </c>
+      <c r="AQ3">
+        <v>4.634013605442177</v>
       </c>
     </row>
     <row r="4">
@@ -823,118 +847,871 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Hainan Haide Capital Management Co., Ltd. (SZSE:000567)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.24</v>
+      </c>
+      <c r="E4">
+        <v>0.26</v>
+      </c>
+      <c r="G4">
+        <v>0.8698579369981468</v>
+      </c>
+      <c r="H4">
+        <v>0.8628783199505867</v>
+      </c>
+      <c r="I4">
+        <v>0.7974058060531192</v>
+      </c>
+      <c r="J4">
+        <v>0.7108909488968954</v>
+      </c>
+      <c r="K4">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="L4">
+        <v>0.5534280420012353</v>
+      </c>
+      <c r="M4">
+        <v>114.5</v>
+      </c>
+      <c r="N4">
+        <v>0.06260251503553854</v>
+      </c>
+      <c r="O4">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="P4">
+        <v>114.5</v>
+      </c>
+      <c r="Q4">
+        <v>0.06260251503553854</v>
+      </c>
+      <c r="R4">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>11.8</v>
+      </c>
+      <c r="V4">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="W4">
+        <v>0.1221374045801527</v>
+      </c>
+      <c r="X4">
+        <v>0.0784607912539228</v>
+      </c>
+      <c r="Y4">
+        <v>0.04367661332622987</v>
+      </c>
+      <c r="Z4">
+        <v>0.1364604896731691</v>
+      </c>
+      <c r="AA4">
+        <v>0.09700852699069419</v>
+      </c>
+      <c r="AB4">
+        <v>0.07145597306660695</v>
+      </c>
+      <c r="AC4">
+        <v>0.02555255392408724</v>
+      </c>
+      <c r="AD4">
+        <v>517.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>517.8</v>
+      </c>
+      <c r="AG4">
+        <v>505.9999999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.2206408726776887</v>
+      </c>
+      <c r="AI4">
+        <v>0.4007119640922458</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2167023554603854</v>
+      </c>
+      <c r="AK4">
+        <v>0.3951890034364261</v>
+      </c>
+      <c r="AL4">
+        <v>34.7</v>
+      </c>
+      <c r="AM4">
+        <v>32.19</v>
+      </c>
+      <c r="AN4">
+        <v>4.013953488372093</v>
+      </c>
+      <c r="AO4">
+        <v>3.720461095100864</v>
+      </c>
+      <c r="AP4">
+        <v>3.922480620155038</v>
+      </c>
+      <c r="AQ4">
+        <v>4.010562286424355</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J-Yuan Trust Co., Ltd. (SHSE:600816)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.367</v>
+      </c>
+      <c r="G5">
+        <v>0.4011220196353437</v>
+      </c>
+      <c r="H5">
+        <v>0.4011220196353437</v>
+      </c>
+      <c r="I5">
+        <v>0.4039270687237027</v>
+      </c>
+      <c r="J5">
+        <v>0.4039270687237027</v>
+      </c>
+      <c r="K5">
+        <v>7.07</v>
+      </c>
+      <c r="L5">
+        <v>0.09915848527349229</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>13.6</v>
+      </c>
+      <c r="V5">
+        <v>0.002881050736150831</v>
+      </c>
+      <c r="W5">
+        <v>0.004001584786053883</v>
+      </c>
+      <c r="X5">
+        <v>0.07274366029337254</v>
+      </c>
+      <c r="Y5">
+        <v>-0.06874207550731866</v>
+      </c>
+      <c r="Z5">
+        <v>0.05348664671732269</v>
+      </c>
+      <c r="AA5">
+        <v>0.02160470442438841</v>
+      </c>
+      <c r="AB5">
+        <v>0.07273962993075585</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05113492550636744</v>
+      </c>
+      <c r="AD5">
+        <v>0.731</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0.731</v>
+      </c>
+      <c r="AG5">
+        <v>-12.869</v>
+      </c>
+      <c r="AH5">
+        <v>0.0001548325002525824</v>
+      </c>
+      <c r="AI5">
+        <v>0.0003582049765500695</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.002733646711052756</v>
+      </c>
+      <c r="AK5">
+        <v>-0.006348381037042006</v>
+      </c>
+      <c r="AL5">
+        <v>0.218</v>
+      </c>
+      <c r="AM5">
+        <v>-22.582</v>
+      </c>
+      <c r="AN5">
+        <v>0.02547038327526132</v>
+      </c>
+      <c r="AO5">
+        <v>132.1100917431193</v>
+      </c>
+      <c r="AP5">
+        <v>-0.448397212543554</v>
+      </c>
+      <c r="AQ5">
+        <v>-1.275352050305553</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>China Cinda Asset Management Co., Ltd. (SEHK:1359)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.0727</v>
+      </c>
+      <c r="E6">
+        <v>-0.202</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>537.9</v>
+      </c>
+      <c r="L6">
+        <v>0.1626598929511022</v>
+      </c>
+      <c r="M6">
+        <v>228.987</v>
+      </c>
+      <c r="N6">
+        <v>0.03669663461538462</v>
+      </c>
+      <c r="O6">
+        <v>0.4257055214723927</v>
+      </c>
+      <c r="P6">
+        <v>228.987</v>
+      </c>
+      <c r="Q6">
+        <v>0.03669663461538462</v>
+      </c>
+      <c r="R6">
+        <v>0.4257055214723927</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="V6">
+        <v>0.01224358974358974</v>
+      </c>
+      <c r="W6">
+        <v>0.02149270191112834</v>
+      </c>
+      <c r="X6">
+        <v>0.4704799155181024</v>
+      </c>
+      <c r="Y6">
+        <v>-0.448987213606974</v>
+      </c>
+      <c r="Z6">
+        <v>0.0216107310621012</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06798516513732292</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06798516513732292</v>
+      </c>
+      <c r="AD6">
+        <v>122833.2</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>122833.2</v>
+      </c>
+      <c r="AG6">
+        <v>122756.8</v>
+      </c>
+      <c r="AH6">
+        <v>0.9516553397606939</v>
+      </c>
+      <c r="AI6">
+        <v>0.8038369568204931</v>
+      </c>
+      <c r="AJ6">
+        <v>0.9516267070190888</v>
+      </c>
+      <c r="AK6">
+        <v>0.8037388317591182</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>China CITIC Financial Asset Management Co., Ltd. (SEHK:2799)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D7">
         <v>-0.255</v>
       </c>
-      <c r="E4">
+      <c r="E7">
         <v>0.224</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>1650.5</v>
       </c>
-      <c r="L4">
+      <c r="L7">
         <v>1.317448914431673</v>
       </c>
-      <c r="M4">
+      <c r="M7">
         <v>129.3</v>
       </c>
-      <c r="N4">
+      <c r="N7">
         <v>0.01925482487491065</v>
       </c>
-      <c r="O4">
+      <c r="O7">
         <v>0.07833989700090882</v>
       </c>
-      <c r="P4">
+      <c r="P7">
         <v>129.3</v>
       </c>
-      <c r="Q4">
+      <c r="Q7">
         <v>0.01925482487491065</v>
       </c>
-      <c r="R4">
+      <c r="R7">
         <v>0.07833989700090882</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
         <v>0.01</v>
       </c>
-      <c r="V4">
+      <c r="V7">
         <v>1.489158923040267E-06</v>
       </c>
-      <c r="W4">
+      <c r="W7">
         <v>0.2915717137456498</v>
       </c>
-      <c r="X4">
-        <v>0.4303956223629298</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1388239086172799</v>
-      </c>
-      <c r="Z4">
+      <c r="X7">
+        <v>0.4302258204014321</v>
+      </c>
+      <c r="Y7">
+        <v>-0.1386541066557823</v>
+      </c>
+      <c r="Z7">
         <v>0.01031742231655482</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07043357817699626</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07043357817699626</v>
-      </c>
-      <c r="AD4">
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.07042449424558339</v>
+      </c>
+      <c r="AC7">
+        <v>-0.07042449424558339</v>
+      </c>
+      <c r="AD7">
         <v>118809.1</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
         <v>118809.1</v>
       </c>
-      <c r="AG4">
+      <c r="AG7">
         <v>118809.09</v>
       </c>
-      <c r="AH4">
+      <c r="AH7">
         <v>0.9465027887030639</v>
       </c>
-      <c r="AI4">
+      <c r="AI7">
         <v>0.9424663597803936</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ7">
         <v>0.9465027844411628</v>
       </c>
-      <c r="AK4">
+      <c r="AK7">
         <v>0.9424663552164734</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kunwu Jiuding Investment Holdings Co., Ltd. (SHSE:600053)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.194</v>
+      </c>
+      <c r="E8">
+        <v>-0.591</v>
+      </c>
+      <c r="G8">
+        <v>0.2864583333333334</v>
+      </c>
+      <c r="H8">
+        <v>0.2864583333333334</v>
+      </c>
+      <c r="I8">
+        <v>0.03177083333333333</v>
+      </c>
+      <c r="J8">
+        <v>0.01588541666666667</v>
+      </c>
+      <c r="K8">
+        <v>0.534</v>
+      </c>
+      <c r="L8">
+        <v>0.01390625</v>
+      </c>
+      <c r="M8">
+        <v>1.21</v>
+      </c>
+      <c r="N8">
+        <v>0.001468803107550376</v>
+      </c>
+      <c r="O8">
+        <v>2.265917602996255</v>
+      </c>
+      <c r="P8">
+        <v>1.21</v>
+      </c>
+      <c r="Q8">
+        <v>0.001468803107550376</v>
+      </c>
+      <c r="R8">
+        <v>2.265917602996255</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>34.4</v>
+      </c>
+      <c r="V8">
+        <v>0.04175770818159748</v>
+      </c>
+      <c r="W8">
+        <v>0.001355329949238579</v>
+      </c>
+      <c r="X8">
+        <v>0.07274053135654038</v>
+      </c>
+      <c r="Y8">
+        <v>-0.0713852014073018</v>
+      </c>
+      <c r="Z8">
+        <v>0.1078106575327082</v>
+      </c>
+      <c r="AA8">
+        <v>0.001712617216014375</v>
+      </c>
+      <c r="AB8">
+        <v>0.07274053135654038</v>
+      </c>
+      <c r="AC8">
+        <v>-0.07102791414052601</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>-34.4</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.04357740055738536</v>
+      </c>
+      <c r="AK8">
+        <v>-0.09026502230385725</v>
+      </c>
+      <c r="AL8">
+        <v>0.992</v>
+      </c>
+      <c r="AM8">
+        <v>-4.818</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>1.229838709677419</v>
+      </c>
+      <c r="AP8">
+        <v>-23.40136054421769</v>
+      </c>
+      <c r="AQ8">
+        <v>-0.2532171025321711</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Shandong International Trust Co., Ltd. (SEHK:1697)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.06909999999999999</v>
+      </c>
+      <c r="E9">
+        <v>-0.276</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>21.2</v>
+      </c>
+      <c r="L9">
+        <v>0.2003780718336484</v>
+      </c>
+      <c r="M9">
+        <v>7.46</v>
+      </c>
+      <c r="N9">
+        <v>0.03189397178281317</v>
+      </c>
+      <c r="O9">
+        <v>0.3518867924528302</v>
+      </c>
+      <c r="P9">
+        <v>7.46</v>
+      </c>
+      <c r="Q9">
+        <v>0.03189397178281317</v>
+      </c>
+      <c r="R9">
+        <v>0.3518867924528302</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>80</v>
+      </c>
+      <c r="V9">
+        <v>0.3420265070542967</v>
+      </c>
+      <c r="W9">
+        <v>0.01383902343495006</v>
+      </c>
+      <c r="X9">
+        <v>0.07960812084834765</v>
+      </c>
+      <c r="Y9">
+        <v>-0.06576909741339759</v>
+      </c>
+      <c r="Z9">
+        <v>0.06605894105894106</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.07173931290576911</v>
+      </c>
+      <c r="AC9">
+        <v>-0.07173931290576911</v>
+      </c>
+      <c r="AD9">
+        <v>79.5</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>79.5</v>
+      </c>
+      <c r="AG9">
+        <v>-0.5</v>
+      </c>
+      <c r="AH9">
+        <v>0.2536694320357371</v>
+      </c>
+      <c r="AI9">
+        <v>0.04881493307134963</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.002142245072836333</v>
+      </c>
+      <c r="AK9">
+        <v>-0.0003228722717293039</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tian Tu Capital Co., Ltd. (SEHK:1973)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>-195.3</v>
+      </c>
+      <c r="M10">
+        <v>26.71</v>
+      </c>
+      <c r="N10">
+        <v>0.0829245575908103</v>
+      </c>
+      <c r="O10">
+        <v>-0.1367639528929852</v>
+      </c>
+      <c r="P10">
+        <v>7.01</v>
+      </c>
+      <c r="Q10">
+        <v>0.02176342750698541</v>
+      </c>
+      <c r="R10">
+        <v>-0.03589349718381976</v>
+      </c>
+      <c r="S10">
+        <v>19.7</v>
+      </c>
+      <c r="T10">
+        <v>0.7375514788468739</v>
+      </c>
+      <c r="U10">
+        <v>140.8</v>
+      </c>
+      <c r="V10">
+        <v>0.4371313256752561</v>
+      </c>
+      <c r="W10">
+        <v>-0.2000204834084392</v>
+      </c>
+      <c r="X10">
+        <v>0.08161058211829482</v>
+      </c>
+      <c r="Y10">
+        <v>-0.281631065526734</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>-0.2008084887566013</v>
+      </c>
+      <c r="AB10">
+        <v>0.07153643739404553</v>
+      </c>
+      <c r="AC10">
+        <v>-0.2723449261506469</v>
+      </c>
+      <c r="AD10">
+        <v>141.4</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>141.4</v>
+      </c>
+      <c r="AG10">
+        <v>0.5999999999999943</v>
+      </c>
+      <c r="AH10">
+        <v>0.3050701186623517</v>
+      </c>
+      <c r="AI10">
+        <v>0.1347821942617481</v>
+      </c>
+      <c r="AJ10">
+        <v>0.001859312054539802</v>
+      </c>
+      <c r="AK10">
+        <v>0.0006605746999889841</v>
+      </c>
+      <c r="AL10">
+        <v>9.5</v>
+      </c>
+      <c r="AM10">
+        <v>8.02</v>
+      </c>
+      <c r="AN10">
+        <v>-0.6607476635514019</v>
+      </c>
+      <c r="AO10">
+        <v>-22.52631578947368</v>
+      </c>
+      <c r="AP10">
+        <v>-0.002803738317756983</v>
+      </c>
+      <c r="AQ10">
+        <v>-26.68329177057357</v>
       </c>
     </row>
   </sheetData>
